--- a/artfynd/A 11705-2024 artfynd.xlsx
+++ b/artfynd/A 11705-2024 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>131257646</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131256691</v>
+        <v>131257424</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,39 +1038,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488667</v>
+        <v>488876</v>
       </c>
       <c r="R5" t="n">
-        <v>6665262</v>
+        <v>6665177</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,7 +1097,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,12 +1107,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,7 +1139,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131260583</v>
+        <v>131256691</v>
       </c>
       <c r="B6" t="n">
         <v>57884</v>
@@ -1175,7 +1170,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1184,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488834</v>
+        <v>488667</v>
       </c>
       <c r="R6" t="n">
-        <v>6665228</v>
+        <v>6665262</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1219,7 +1214,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1229,12 +1224,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131257424</v>
+        <v>131260583</v>
       </c>
       <c r="B7" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,34 +1267,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488876</v>
+        <v>488834</v>
       </c>
       <c r="R7" t="n">
-        <v>6665177</v>
+        <v>6665228</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1341,12 +1341,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,7 +1376,7 @@
         <v>131255793</v>
       </c>
       <c r="B8" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131256423</v>
+        <v>131257188</v>
       </c>
       <c r="B9" t="n">
-        <v>57881</v>
+        <v>91834</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,51 +1492,33 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488671</v>
+        <v>488804</v>
       </c>
       <c r="R9" t="n">
-        <v>6665267</v>
+        <v>6665288</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1565,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1575,7 +1557,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1602,10 +1589,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131257188</v>
+        <v>131256423</v>
       </c>
       <c r="B10" t="n">
-        <v>91833</v>
+        <v>57881</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,33 +1600,51 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488804</v>
+        <v>488671</v>
       </c>
       <c r="R10" t="n">
-        <v>6665288</v>
+        <v>6665267</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1668,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,12 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,7 +1713,7 @@
         <v>131256730</v>
       </c>
       <c r="B11" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>131257520</v>
       </c>
       <c r="B12" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131255096</v>
+        <v>131257479</v>
       </c>
       <c r="B16" t="n">
-        <v>79245</v>
+        <v>91834</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2296,23 +2296,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2320,10 +2316,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488961</v>
+        <v>488908</v>
       </c>
       <c r="R16" t="n">
-        <v>6665423</v>
+        <v>6665154</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2355,7 +2351,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2365,12 +2361,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Stambrott. Hängande låga.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2397,10 +2393,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131257479</v>
+        <v>131255096</v>
       </c>
       <c r="B17" t="n">
-        <v>91833</v>
+        <v>79246</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2408,19 +2404,23 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488908</v>
+        <v>488961</v>
       </c>
       <c r="R17" t="n">
-        <v>6665154</v>
+        <v>6665423</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Stambrott. Hängande låga.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2508,7 +2508,7 @@
         <v>131256750</v>
       </c>
       <c r="B18" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>131256401</v>
       </c>
       <c r="B19" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>131256403</v>
       </c>
       <c r="B20" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>131257637</v>
       </c>
       <c r="B21" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>131257316</v>
       </c>
       <c r="B22" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>131255771</v>
       </c>
       <c r="B23" t="n">
-        <v>81230</v>
+        <v>81231</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>131257642</v>
       </c>
       <c r="B24" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>131257045</v>
       </c>
       <c r="B25" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>131257650</v>
       </c>
       <c r="B26" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>131257544</v>
       </c>
       <c r="B27" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>131256649</v>
       </c>
       <c r="B28" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>131255910</v>
       </c>
       <c r="B29" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>131258531</v>
       </c>
       <c r="B30" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>131258537</v>
       </c>
       <c r="B32" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>131255108</v>
       </c>
       <c r="B33" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>131257913</v>
       </c>
       <c r="B35" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131257385</v>
+        <v>131260531</v>
       </c>
       <c r="B36" t="n">
-        <v>91833</v>
+        <v>79246</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4537,19 +4537,23 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4557,10 +4561,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488876</v>
+        <v>488786</v>
       </c>
       <c r="R36" t="n">
-        <v>6665194</v>
+        <v>6665188</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4592,7 +4596,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4602,12 +4606,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Lågstubbe.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4634,10 +4638,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131260531</v>
+        <v>131256459</v>
       </c>
       <c r="B37" t="n">
-        <v>79245</v>
+        <v>57881</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4645,34 +4649,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488786</v>
+        <v>488669</v>
       </c>
       <c r="R37" t="n">
-        <v>6665188</v>
+        <v>6665268</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4704,7 +4713,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4714,12 +4723,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Färska och äldre hack.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4746,10 +4755,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131256459</v>
+        <v>131257385</v>
       </c>
       <c r="B38" t="n">
-        <v>57881</v>
+        <v>91834</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4757,39 +4766,30 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488669</v>
+        <v>488876</v>
       </c>
       <c r="R38" t="n">
-        <v>6665268</v>
+        <v>6665194</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska och äldre hack.</t>
+          <t>Lågstubbe.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4866,7 +4866,7 @@
         <v>131257731</v>
       </c>
       <c r="B39" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>131257440</v>
       </c>
       <c r="B40" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>131257035</v>
       </c>
       <c r="B41" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>131273946</v>
       </c>
       <c r="B43" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>131273991</v>
       </c>
       <c r="B44" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>131273940</v>
       </c>
       <c r="B45" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 11705-2024 artfynd.xlsx
+++ b/artfynd/A 11705-2024 artfynd.xlsx
@@ -1481,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131257188</v>
+        <v>131256423</v>
       </c>
       <c r="B9" t="n">
-        <v>91834</v>
+        <v>57881</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,33 +1492,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488804</v>
+        <v>488671</v>
       </c>
       <c r="R9" t="n">
-        <v>6665288</v>
+        <v>6665267</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1547,7 +1565,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,12 +1575,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,10 +1602,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131256423</v>
+        <v>131257188</v>
       </c>
       <c r="B10" t="n">
-        <v>57881</v>
+        <v>91834</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,51 +1613,33 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488671</v>
+        <v>488804</v>
       </c>
       <c r="R10" t="n">
-        <v>6665267</v>
+        <v>6665288</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1678,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2953,10 +2953,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131257316</v>
+        <v>131255771</v>
       </c>
       <c r="B22" t="n">
-        <v>79246</v>
+        <v>81231</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2964,21 +2964,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488852</v>
+        <v>488818</v>
       </c>
       <c r="R22" t="n">
-        <v>6665209</v>
+        <v>6665110</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3033,12 +3033,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3065,10 +3060,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131255771</v>
+        <v>131257316</v>
       </c>
       <c r="B23" t="n">
-        <v>81231</v>
+        <v>79246</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3076,21 +3071,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3100,10 +3095,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488818</v>
+        <v>488852</v>
       </c>
       <c r="R23" t="n">
-        <v>6665110</v>
+        <v>6665209</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3135,7 +3130,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3145,7 +3140,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4526,10 +4526,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131260531</v>
+        <v>131257385</v>
       </c>
       <c r="B36" t="n">
-        <v>79246</v>
+        <v>91834</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4537,23 +4537,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4561,10 +4557,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488786</v>
+        <v>488876</v>
       </c>
       <c r="R36" t="n">
-        <v>6665188</v>
+        <v>6665194</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4596,7 +4592,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4606,12 +4602,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Lågstubbe.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4638,10 +4634,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131256459</v>
+        <v>131260531</v>
       </c>
       <c r="B37" t="n">
-        <v>57881</v>
+        <v>79246</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4649,39 +4645,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488669</v>
+        <v>488786</v>
       </c>
       <c r="R37" t="n">
-        <v>6665268</v>
+        <v>6665188</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4713,7 +4704,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4723,12 +4714,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska och äldre hack.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4755,10 +4746,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131257385</v>
+        <v>131256459</v>
       </c>
       <c r="B38" t="n">
-        <v>91834</v>
+        <v>57881</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4766,30 +4757,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488876</v>
+        <v>488669</v>
       </c>
       <c r="R38" t="n">
-        <v>6665194</v>
+        <v>6665268</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Lågstubbe.</t>
+          <t>Färska och äldre hack.</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 11705-2024 artfynd.xlsx
+++ b/artfynd/A 11705-2024 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>131257487</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131257646</v>
       </c>
       <c r="B4" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>131257424</v>
       </c>
       <c r="B5" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131256691</v>
+        <v>131255793</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>91836</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1150,39 +1150,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488667</v>
+        <v>488817</v>
       </c>
       <c r="R6" t="n">
-        <v>6665262</v>
+        <v>6665110</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1214,7 +1205,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1224,12 +1215,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,7 +1250,7 @@
         <v>131260583</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131255793</v>
+        <v>131256691</v>
       </c>
       <c r="B8" t="n">
-        <v>91834</v>
+        <v>57886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1384,30 +1375,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488817</v>
+        <v>488667</v>
       </c>
       <c r="R8" t="n">
-        <v>6665110</v>
+        <v>6665262</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131256423</v>
+        <v>131257188</v>
       </c>
       <c r="B9" t="n">
-        <v>57881</v>
+        <v>91836</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,51 +1492,33 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488671</v>
+        <v>488804</v>
       </c>
       <c r="R9" t="n">
-        <v>6665267</v>
+        <v>6665288</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1565,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1575,7 +1557,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1602,10 +1589,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131257188</v>
+        <v>131256423</v>
       </c>
       <c r="B10" t="n">
-        <v>91834</v>
+        <v>57883</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,33 +1600,51 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488804</v>
+        <v>488671</v>
       </c>
       <c r="R10" t="n">
-        <v>6665288</v>
+        <v>6665267</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1668,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,12 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,7 +1713,7 @@
         <v>131256730</v>
       </c>
       <c r="B11" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>131257520</v>
       </c>
       <c r="B12" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>131260641</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>131257290</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>131256673</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>131257479</v>
       </c>
       <c r="B16" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>131255096</v>
       </c>
       <c r="B17" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>131256750</v>
       </c>
       <c r="B18" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>131256401</v>
       </c>
       <c r="B19" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>131256403</v>
       </c>
       <c r="B20" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>131257637</v>
       </c>
       <c r="B21" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>131255771</v>
       </c>
       <c r="B22" t="n">
-        <v>81231</v>
+        <v>81233</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>131257316</v>
       </c>
       <c r="B23" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3172,10 +3172,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131257642</v>
+        <v>131257045</v>
       </c>
       <c r="B24" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3207,10 +3207,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488913</v>
+        <v>488760</v>
       </c>
       <c r="R24" t="n">
-        <v>6665191</v>
+        <v>6665302</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3252,12 +3252,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3284,10 +3284,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131257045</v>
+        <v>131257642</v>
       </c>
       <c r="B25" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3319,10 +3319,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488760</v>
+        <v>488913</v>
       </c>
       <c r="R25" t="n">
-        <v>6665302</v>
+        <v>6665191</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3399,7 +3399,7 @@
         <v>131257650</v>
       </c>
       <c r="B26" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>131257544</v>
       </c>
       <c r="B27" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>131256649</v>
       </c>
       <c r="B28" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>131255910</v>
       </c>
       <c r="B29" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>131258531</v>
       </c>
       <c r="B30" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>131257239</v>
       </c>
       <c r="B31" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>131258537</v>
       </c>
       <c r="B32" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>131255108</v>
       </c>
       <c r="B33" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>131257659</v>
       </c>
       <c r="B34" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>131257913</v>
       </c>
       <c r="B35" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>131257385</v>
       </c>
       <c r="B36" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>131260531</v>
       </c>
       <c r="B37" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>131256459</v>
       </c>
       <c r="B38" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4863,10 +4863,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131257731</v>
+        <v>131257440</v>
       </c>
       <c r="B39" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488874</v>
+        <v>488885</v>
       </c>
       <c r="R39" t="n">
-        <v>6665272</v>
+        <v>6665181</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4975,10 +4975,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131257440</v>
+        <v>131257731</v>
       </c>
       <c r="B40" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488885</v>
+        <v>488874</v>
       </c>
       <c r="R40" t="n">
-        <v>6665181</v>
+        <v>6665272</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5090,7 +5090,7 @@
         <v>131257035</v>
       </c>
       <c r="B41" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>131257343</v>
       </c>
       <c r="B42" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>131273946</v>
       </c>
       <c r="B43" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>131273991</v>
       </c>
       <c r="B44" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>131273940</v>
       </c>
       <c r="B45" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 11705-2024 artfynd.xlsx
+++ b/artfynd/A 11705-2024 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>131257487</v>
       </c>
       <c r="B3" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131257646</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>131257424</v>
       </c>
       <c r="B5" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>131255793</v>
       </c>
       <c r="B6" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>131260583</v>
       </c>
       <c r="B7" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>131256691</v>
       </c>
       <c r="B8" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131257188</v>
+        <v>131256423</v>
       </c>
       <c r="B9" t="n">
-        <v>91836</v>
+        <v>57884</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,33 +1492,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488804</v>
+        <v>488671</v>
       </c>
       <c r="R9" t="n">
-        <v>6665288</v>
+        <v>6665267</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1547,7 +1565,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,12 +1575,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,10 +1602,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131256423</v>
+        <v>131257188</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
+        <v>91837</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,51 +1613,33 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488671</v>
+        <v>488804</v>
       </c>
       <c r="R10" t="n">
-        <v>6665267</v>
+        <v>6665288</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1678,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131256730</v>
+        <v>131256673</v>
       </c>
       <c r="B11" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1721,34 +1721,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488689</v>
+        <v>488652</v>
       </c>
       <c r="R11" t="n">
-        <v>6665231</v>
+        <v>6665282</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1780,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1790,12 +1795,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131257520</v>
+        <v>131256730</v>
       </c>
       <c r="B12" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1857,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488939</v>
+        <v>488689</v>
       </c>
       <c r="R12" t="n">
-        <v>6665149</v>
+        <v>6665231</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1892,7 +1897,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1902,12 +1907,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,10 +1939,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131260641</v>
+        <v>131257520</v>
       </c>
       <c r="B13" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1945,39 +1950,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488859</v>
+        <v>488939</v>
       </c>
       <c r="R13" t="n">
-        <v>6665292</v>
+        <v>6665149</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,10 +2051,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131257290</v>
+        <v>131260641</v>
       </c>
       <c r="B14" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488842</v>
+        <v>488859</v>
       </c>
       <c r="R14" t="n">
-        <v>6665224</v>
+        <v>6665292</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,10 +2168,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131256673</v>
+        <v>131257290</v>
       </c>
       <c r="B15" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488652</v>
+        <v>488842</v>
       </c>
       <c r="R15" t="n">
-        <v>6665282</v>
+        <v>6665224</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131257479</v>
+        <v>131255096</v>
       </c>
       <c r="B16" t="n">
-        <v>91836</v>
+        <v>79249</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2296,19 +2296,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2316,10 +2320,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488908</v>
+        <v>488961</v>
       </c>
       <c r="R16" t="n">
-        <v>6665154</v>
+        <v>6665423</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2351,7 +2355,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2361,12 +2365,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Stambrott. Hängande låga.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2393,10 +2397,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131255096</v>
+        <v>131256750</v>
       </c>
       <c r="B17" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2428,10 +2432,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488961</v>
+        <v>488704</v>
       </c>
       <c r="R17" t="n">
-        <v>6665423</v>
+        <v>6665241</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2463,7 +2467,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2473,12 +2477,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2505,10 +2509,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131256750</v>
+        <v>131257479</v>
       </c>
       <c r="B18" t="n">
-        <v>79248</v>
+        <v>91837</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,23 +2520,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488704</v>
+        <v>488908</v>
       </c>
       <c r="R18" t="n">
-        <v>6665241</v>
+        <v>6665154</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Stambrott. Hängande låga.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2620,7 +2620,7 @@
         <v>131256401</v>
       </c>
       <c r="B19" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>131256403</v>
       </c>
       <c r="B20" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>131257637</v>
       </c>
       <c r="B21" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2953,10 +2953,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131255771</v>
+        <v>131257316</v>
       </c>
       <c r="B22" t="n">
-        <v>81233</v>
+        <v>79249</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2964,21 +2964,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488818</v>
+        <v>488852</v>
       </c>
       <c r="R22" t="n">
-        <v>6665110</v>
+        <v>6665209</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3033,7 +3033,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3060,10 +3065,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131257316</v>
+        <v>131255771</v>
       </c>
       <c r="B23" t="n">
-        <v>79248</v>
+        <v>81234</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3071,21 +3076,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3095,10 +3100,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488852</v>
+        <v>488818</v>
       </c>
       <c r="R23" t="n">
-        <v>6665209</v>
+        <v>6665110</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3130,7 +3135,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3140,12 +3145,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3172,10 +3172,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131257045</v>
+        <v>131257642</v>
       </c>
       <c r="B24" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3207,10 +3207,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488760</v>
+        <v>488913</v>
       </c>
       <c r="R24" t="n">
-        <v>6665302</v>
+        <v>6665191</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3252,12 +3252,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3284,10 +3284,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131257642</v>
+        <v>131257045</v>
       </c>
       <c r="B25" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3319,10 +3319,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488913</v>
+        <v>488760</v>
       </c>
       <c r="R25" t="n">
-        <v>6665191</v>
+        <v>6665302</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3399,7 +3399,7 @@
         <v>131257650</v>
       </c>
       <c r="B26" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>131257544</v>
       </c>
       <c r="B27" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>131256649</v>
       </c>
       <c r="B28" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>131255910</v>
       </c>
       <c r="B29" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>131258531</v>
       </c>
       <c r="B30" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>131257239</v>
       </c>
       <c r="B31" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>131258537</v>
       </c>
       <c r="B32" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>131255108</v>
       </c>
       <c r="B33" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>131257659</v>
       </c>
       <c r="B34" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>131257913</v>
       </c>
       <c r="B35" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131257385</v>
+        <v>131256459</v>
       </c>
       <c r="B36" t="n">
-        <v>91836</v>
+        <v>57884</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4537,30 +4537,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488876</v>
+        <v>488669</v>
       </c>
       <c r="R36" t="n">
-        <v>6665194</v>
+        <v>6665268</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4592,7 +4601,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4602,12 +4611,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Lågstubbe.</t>
+          <t>Färska och äldre hack.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4634,10 +4643,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131260531</v>
+        <v>131257385</v>
       </c>
       <c r="B37" t="n">
-        <v>79248</v>
+        <v>91837</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4645,23 +4654,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4669,10 +4674,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488786</v>
+        <v>488876</v>
       </c>
       <c r="R37" t="n">
-        <v>6665188</v>
+        <v>6665194</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4704,7 +4709,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4714,12 +4719,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Lågstubbe.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4746,10 +4751,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131256459</v>
+        <v>131260531</v>
       </c>
       <c r="B38" t="n">
-        <v>57883</v>
+        <v>79249</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4757,39 +4762,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488669</v>
+        <v>488786</v>
       </c>
       <c r="R38" t="n">
-        <v>6665268</v>
+        <v>6665188</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska och äldre hack.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4863,10 +4863,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131257440</v>
+        <v>131257731</v>
       </c>
       <c r="B39" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488885</v>
+        <v>488874</v>
       </c>
       <c r="R39" t="n">
-        <v>6665181</v>
+        <v>6665272</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4975,10 +4975,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131257731</v>
+        <v>131257440</v>
       </c>
       <c r="B40" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488874</v>
+        <v>488885</v>
       </c>
       <c r="R40" t="n">
-        <v>6665272</v>
+        <v>6665181</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5090,7 +5090,7 @@
         <v>131257035</v>
       </c>
       <c r="B41" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>131257343</v>
       </c>
       <c r="B42" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>131273946</v>
       </c>
       <c r="B43" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>131273991</v>
       </c>
       <c r="B44" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>131273940</v>
       </c>
       <c r="B45" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 11705-2024 artfynd.xlsx
+++ b/artfynd/A 11705-2024 artfynd.xlsx
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131255793</v>
+        <v>131256691</v>
       </c>
       <c r="B6" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1150,30 +1150,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488817</v>
+        <v>488667</v>
       </c>
       <c r="R6" t="n">
-        <v>6665110</v>
+        <v>6665262</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,7 +1214,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1215,12 +1224,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1364,10 +1373,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131256691</v>
+        <v>131255793</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>91837</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,39 +1384,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488667</v>
+        <v>488817</v>
       </c>
       <c r="R8" t="n">
-        <v>6665262</v>
+        <v>6665110</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131256423</v>
+        <v>131257188</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>91837</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,51 +1492,33 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488671</v>
+        <v>488804</v>
       </c>
       <c r="R9" t="n">
-        <v>6665267</v>
+        <v>6665288</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1565,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1575,7 +1557,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1602,10 +1589,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131257188</v>
+        <v>131256423</v>
       </c>
       <c r="B10" t="n">
-        <v>91837</v>
+        <v>57884</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,33 +1600,51 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488804</v>
+        <v>488671</v>
       </c>
       <c r="R10" t="n">
-        <v>6665288</v>
+        <v>6665267</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1668,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,12 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,7 +1710,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131256673</v>
+        <v>131260641</v>
       </c>
       <c r="B11" t="n">
         <v>57887</v>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488652</v>
+        <v>488859</v>
       </c>
       <c r="R11" t="n">
-        <v>6665282</v>
+        <v>6665292</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131256730</v>
+        <v>131257290</v>
       </c>
       <c r="B12" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,34 +1838,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488689</v>
+        <v>488842</v>
       </c>
       <c r="R12" t="n">
-        <v>6665231</v>
+        <v>6665224</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1897,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,12 +1912,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1939,10 +1944,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131257520</v>
+        <v>131256673</v>
       </c>
       <c r="B13" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1950,34 +1955,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488939</v>
+        <v>488652</v>
       </c>
       <c r="R13" t="n">
-        <v>6665149</v>
+        <v>6665282</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2009,7 +2019,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2019,12 +2029,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,10 +2061,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131260641</v>
+        <v>131256730</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2062,39 +2072,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488859</v>
+        <v>488689</v>
       </c>
       <c r="R14" t="n">
-        <v>6665292</v>
+        <v>6665231</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2126,7 +2131,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2136,12 +2141,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,10 +2173,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131257290</v>
+        <v>131257520</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2179,39 +2184,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488842</v>
+        <v>488939</v>
       </c>
       <c r="R15" t="n">
-        <v>6665224</v>
+        <v>6665149</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131255096</v>
+        <v>131257479</v>
       </c>
       <c r="B16" t="n">
-        <v>79249</v>
+        <v>91837</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2296,23 +2296,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2320,10 +2316,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488961</v>
+        <v>488908</v>
       </c>
       <c r="R16" t="n">
-        <v>6665423</v>
+        <v>6665154</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2355,7 +2351,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2365,12 +2361,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Stambrott. Hängande låga.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2397,7 +2393,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131256750</v>
+        <v>131255096</v>
       </c>
       <c r="B17" t="n">
         <v>79249</v>
@@ -2432,10 +2428,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488704</v>
+        <v>488961</v>
       </c>
       <c r="R17" t="n">
-        <v>6665241</v>
+        <v>6665423</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2467,7 +2463,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2477,12 +2473,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2509,10 +2505,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131257479</v>
+        <v>131256750</v>
       </c>
       <c r="B18" t="n">
-        <v>91837</v>
+        <v>79249</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2520,19 +2516,23 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488908</v>
+        <v>488704</v>
       </c>
       <c r="R18" t="n">
-        <v>6665154</v>
+        <v>6665241</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Stambrott. Hängande låga.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2953,10 +2953,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131257316</v>
+        <v>131255771</v>
       </c>
       <c r="B22" t="n">
-        <v>79249</v>
+        <v>81234</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2964,21 +2964,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488852</v>
+        <v>488818</v>
       </c>
       <c r="R22" t="n">
-        <v>6665209</v>
+        <v>6665110</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3033,12 +3033,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3065,10 +3060,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131255771</v>
+        <v>131257316</v>
       </c>
       <c r="B23" t="n">
-        <v>81234</v>
+        <v>79249</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3076,21 +3071,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3100,10 +3095,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488818</v>
+        <v>488852</v>
       </c>
       <c r="R23" t="n">
-        <v>6665110</v>
+        <v>6665209</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3135,7 +3130,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3145,7 +3140,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4526,10 +4526,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131256459</v>
+        <v>131260531</v>
       </c>
       <c r="B36" t="n">
-        <v>57884</v>
+        <v>79249</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4537,39 +4537,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488669</v>
+        <v>488786</v>
       </c>
       <c r="R36" t="n">
-        <v>6665268</v>
+        <v>6665188</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4601,7 +4596,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4611,12 +4606,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska och äldre hack.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4751,10 +4746,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131260531</v>
+        <v>131256459</v>
       </c>
       <c r="B38" t="n">
-        <v>79249</v>
+        <v>57884</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4762,34 +4757,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488786</v>
+        <v>488669</v>
       </c>
       <c r="R38" t="n">
-        <v>6665188</v>
+        <v>6665268</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Färska och äldre hack.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5087,10 +5087,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131257035</v>
+        <v>131257343</v>
       </c>
       <c r="B41" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5098,34 +5098,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488760</v>
+        <v>488872</v>
       </c>
       <c r="R41" t="n">
-        <v>6665301</v>
+        <v>6665191</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5157,7 +5162,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5167,12 +5172,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5199,10 +5204,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131257343</v>
+        <v>131257035</v>
       </c>
       <c r="B42" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5210,39 +5215,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488872</v>
+        <v>488760</v>
       </c>
       <c r="R42" t="n">
-        <v>6665191</v>
+        <v>6665301</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 11705-2024 artfynd.xlsx
+++ b/artfynd/A 11705-2024 artfynd.xlsx
@@ -1027,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131257424</v>
+        <v>131255793</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>91837</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,23 +1038,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1062,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488876</v>
+        <v>488817</v>
       </c>
       <c r="R5" t="n">
-        <v>6665177</v>
+        <v>6665110</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1107,12 +1103,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131256691</v>
+        <v>131257424</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1150,39 +1146,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488667</v>
+        <v>488876</v>
       </c>
       <c r="R6" t="n">
-        <v>6665262</v>
+        <v>6665177</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1214,7 +1205,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1224,12 +1215,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1373,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131255793</v>
+        <v>131256691</v>
       </c>
       <c r="B8" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1384,30 +1375,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488817</v>
+        <v>488667</v>
       </c>
       <c r="R8" t="n">
-        <v>6665110</v>
+        <v>6665262</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1710,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131260641</v>
+        <v>131256730</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1721,39 +1721,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488859</v>
+        <v>488689</v>
       </c>
       <c r="R11" t="n">
-        <v>6665292</v>
+        <v>6665231</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1785,7 +1780,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,12 +1790,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131257290</v>
+        <v>131257520</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,39 +1833,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488842</v>
+        <v>488939</v>
       </c>
       <c r="R12" t="n">
-        <v>6665224</v>
+        <v>6665149</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1902,7 +1892,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,12 +1902,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2061,10 +2051,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131256730</v>
+        <v>131260641</v>
       </c>
       <c r="B14" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2072,34 +2062,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488689</v>
+        <v>488859</v>
       </c>
       <c r="R14" t="n">
-        <v>6665231</v>
+        <v>6665292</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2131,7 +2126,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2141,12 +2136,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,10 +2168,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131257520</v>
+        <v>131257290</v>
       </c>
       <c r="B15" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2184,34 +2179,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488939</v>
+        <v>488842</v>
       </c>
       <c r="R15" t="n">
-        <v>6665149</v>
+        <v>6665224</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2953,10 +2953,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131255771</v>
+        <v>131257316</v>
       </c>
       <c r="B22" t="n">
-        <v>81234</v>
+        <v>79249</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2964,21 +2964,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488818</v>
+        <v>488852</v>
       </c>
       <c r="R22" t="n">
-        <v>6665110</v>
+        <v>6665209</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3033,7 +3033,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3060,10 +3065,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131257316</v>
+        <v>131255771</v>
       </c>
       <c r="B23" t="n">
-        <v>79249</v>
+        <v>81234</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3071,21 +3076,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3095,10 +3100,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488852</v>
+        <v>488818</v>
       </c>
       <c r="R23" t="n">
-        <v>6665209</v>
+        <v>6665110</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3130,7 +3135,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3140,12 +3145,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4526,10 +4526,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131260531</v>
+        <v>131257385</v>
       </c>
       <c r="B36" t="n">
-        <v>79249</v>
+        <v>91837</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4537,23 +4537,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4561,10 +4557,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488786</v>
+        <v>488876</v>
       </c>
       <c r="R36" t="n">
-        <v>6665188</v>
+        <v>6665194</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4596,7 +4592,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4606,12 +4602,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Lågstubbe.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4638,10 +4634,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131257385</v>
+        <v>131260531</v>
       </c>
       <c r="B37" t="n">
-        <v>91837</v>
+        <v>79249</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4649,19 +4645,23 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488876</v>
+        <v>488786</v>
       </c>
       <c r="R37" t="n">
-        <v>6665194</v>
+        <v>6665188</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4714,12 +4714,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Lågstubbe.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5087,10 +5087,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131257343</v>
+        <v>131257035</v>
       </c>
       <c r="B41" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5098,39 +5098,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488872</v>
+        <v>488760</v>
       </c>
       <c r="R41" t="n">
-        <v>6665191</v>
+        <v>6665301</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5162,7 +5157,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5172,12 +5167,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5204,10 +5199,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131257035</v>
+        <v>131257343</v>
       </c>
       <c r="B42" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5215,34 +5210,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488760</v>
+        <v>488872</v>
       </c>
       <c r="R42" t="n">
-        <v>6665301</v>
+        <v>6665191</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 11705-2024 artfynd.xlsx
+++ b/artfynd/A 11705-2024 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>131257487</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131257646</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131255793</v>
+        <v>131256691</v>
       </c>
       <c r="B5" t="n">
-        <v>91837</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,30 +1038,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488817</v>
+        <v>488667</v>
       </c>
       <c r="R5" t="n">
-        <v>6665110</v>
+        <v>6665262</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1093,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,12 +1112,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131257424</v>
+        <v>131260583</v>
       </c>
       <c r="B6" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1146,34 +1155,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488876</v>
+        <v>488834</v>
       </c>
       <c r="R6" t="n">
-        <v>6665177</v>
+        <v>6665228</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,7 +1219,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1215,12 +1229,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131260583</v>
+        <v>131257424</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,39 +1272,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488834</v>
+        <v>488876</v>
       </c>
       <c r="R7" t="n">
-        <v>6665228</v>
+        <v>6665177</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1322,7 +1331,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,12 +1341,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,10 +1373,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131256691</v>
+        <v>131255793</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>91838</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,39 +1384,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488667</v>
+        <v>488817</v>
       </c>
       <c r="R8" t="n">
-        <v>6665262</v>
+        <v>6665110</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,7 +1484,7 @@
         <v>131257188</v>
       </c>
       <c r="B9" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>131256423</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131256730</v>
+        <v>131260641</v>
       </c>
       <c r="B11" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1721,34 +1721,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488689</v>
+        <v>488859</v>
       </c>
       <c r="R11" t="n">
-        <v>6665231</v>
+        <v>6665292</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1780,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1790,12 +1795,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131257520</v>
+        <v>131257290</v>
       </c>
       <c r="B12" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1833,34 +1838,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488939</v>
+        <v>488842</v>
       </c>
       <c r="R12" t="n">
-        <v>6665149</v>
+        <v>6665224</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1892,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1902,12 +1912,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,7 +1947,7 @@
         <v>131256673</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2051,10 +2061,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131260641</v>
+        <v>131256730</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2062,39 +2072,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488859</v>
+        <v>488689</v>
       </c>
       <c r="R14" t="n">
-        <v>6665292</v>
+        <v>6665231</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2126,7 +2131,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2136,12 +2141,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,10 +2173,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131257290</v>
+        <v>131257520</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2179,39 +2184,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488842</v>
+        <v>488939</v>
       </c>
       <c r="R15" t="n">
-        <v>6665224</v>
+        <v>6665149</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131257479</v>
+        <v>131255096</v>
       </c>
       <c r="B16" t="n">
-        <v>91837</v>
+        <v>79250</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2296,19 +2296,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2316,10 +2320,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488908</v>
+        <v>488961</v>
       </c>
       <c r="R16" t="n">
-        <v>6665154</v>
+        <v>6665423</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2351,7 +2355,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2361,12 +2365,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Stambrott. Hängande låga.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2393,10 +2397,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131255096</v>
+        <v>131257479</v>
       </c>
       <c r="B17" t="n">
-        <v>79249</v>
+        <v>91838</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2404,23 +2408,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488961</v>
+        <v>488908</v>
       </c>
       <c r="R17" t="n">
-        <v>6665423</v>
+        <v>6665154</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Stambrott. Hängande låga.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2508,7 +2508,7 @@
         <v>131256750</v>
       </c>
       <c r="B18" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>131256401</v>
       </c>
       <c r="B19" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>131256403</v>
       </c>
       <c r="B20" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>131257637</v>
       </c>
       <c r="B21" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2953,10 +2953,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131257316</v>
+        <v>131255771</v>
       </c>
       <c r="B22" t="n">
-        <v>79249</v>
+        <v>81235</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2964,21 +2964,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488852</v>
+        <v>488818</v>
       </c>
       <c r="R22" t="n">
-        <v>6665209</v>
+        <v>6665110</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3033,12 +3033,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3065,10 +3060,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131255771</v>
+        <v>131257316</v>
       </c>
       <c r="B23" t="n">
-        <v>81234</v>
+        <v>79250</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3076,21 +3071,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3100,10 +3095,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488818</v>
+        <v>488852</v>
       </c>
       <c r="R23" t="n">
-        <v>6665110</v>
+        <v>6665209</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3135,7 +3130,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3145,7 +3140,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3175,7 +3175,7 @@
         <v>131257642</v>
       </c>
       <c r="B24" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>131257045</v>
       </c>
       <c r="B25" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>131257650</v>
       </c>
       <c r="B26" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>131257544</v>
       </c>
       <c r="B27" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>131256649</v>
       </c>
       <c r="B28" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>131255910</v>
       </c>
       <c r="B29" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>131258531</v>
       </c>
       <c r="B30" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>131257239</v>
       </c>
       <c r="B31" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4073,10 +4073,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131258537</v>
+        <v>131257659</v>
       </c>
       <c r="B32" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4084,34 +4084,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488726</v>
+        <v>488901</v>
       </c>
       <c r="R32" t="n">
-        <v>6665209</v>
+        <v>6665222</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4143,7 +4148,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4153,12 +4158,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4185,10 +4190,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131255108</v>
+        <v>131258537</v>
       </c>
       <c r="B33" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4220,10 +4225,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488978</v>
+        <v>488726</v>
       </c>
       <c r="R33" t="n">
-        <v>6665417</v>
+        <v>6665209</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4255,7 +4260,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4265,12 +4270,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4297,10 +4302,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131257659</v>
+        <v>131255108</v>
       </c>
       <c r="B34" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4308,39 +4313,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488901</v>
+        <v>488978</v>
       </c>
       <c r="R34" t="n">
-        <v>6665222</v>
+        <v>6665417</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4417,7 +4417,7 @@
         <v>131257913</v>
       </c>
       <c r="B35" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>131257385</v>
       </c>
       <c r="B36" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>131260531</v>
       </c>
       <c r="B37" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>131256459</v>
       </c>
       <c r="B38" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>131257731</v>
       </c>
       <c r="B39" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>131257440</v>
       </c>
       <c r="B40" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5087,10 +5087,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131257035</v>
+        <v>131257343</v>
       </c>
       <c r="B41" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5098,34 +5098,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488760</v>
+        <v>488872</v>
       </c>
       <c r="R41" t="n">
-        <v>6665301</v>
+        <v>6665191</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5157,7 +5162,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5167,12 +5172,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5199,10 +5204,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131257343</v>
+        <v>131257035</v>
       </c>
       <c r="B42" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5210,39 +5215,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488872</v>
+        <v>488760</v>
       </c>
       <c r="R42" t="n">
-        <v>6665191</v>
+        <v>6665301</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5319,7 +5319,7 @@
         <v>131273946</v>
       </c>
       <c r="B43" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>131273991</v>
       </c>
       <c r="B44" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>131273940</v>
       </c>
       <c r="B45" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 11705-2024 artfynd.xlsx
+++ b/artfynd/A 11705-2024 artfynd.xlsx
@@ -1027,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131256691</v>
+        <v>131257424</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,39 +1038,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488667</v>
+        <v>488876</v>
       </c>
       <c r="R5" t="n">
-        <v>6665262</v>
+        <v>6665177</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,7 +1097,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,12 +1107,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131260583</v>
+        <v>131255793</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>91838</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,39 +1150,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488834</v>
+        <v>488817</v>
       </c>
       <c r="R6" t="n">
-        <v>6665228</v>
+        <v>6665110</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1219,7 +1205,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1229,12 +1215,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131257424</v>
+        <v>131256691</v>
       </c>
       <c r="B7" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,34 +1258,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488876</v>
+        <v>488667</v>
       </c>
       <c r="R7" t="n">
-        <v>6665177</v>
+        <v>6665262</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1331,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1341,12 +1332,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131255793</v>
+        <v>131260583</v>
       </c>
       <c r="B8" t="n">
-        <v>91838</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1384,30 +1375,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488817</v>
+        <v>488834</v>
       </c>
       <c r="R8" t="n">
-        <v>6665110</v>
+        <v>6665228</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131257188</v>
+        <v>131256423</v>
       </c>
       <c r="B9" t="n">
-        <v>91838</v>
+        <v>57885</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,33 +1492,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488804</v>
+        <v>488671</v>
       </c>
       <c r="R9" t="n">
-        <v>6665288</v>
+        <v>6665267</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1547,7 +1565,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,12 +1575,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,10 +1602,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131256423</v>
+        <v>131257188</v>
       </c>
       <c r="B10" t="n">
-        <v>57885</v>
+        <v>91838</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,51 +1613,33 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488671</v>
+        <v>488804</v>
       </c>
       <c r="R10" t="n">
-        <v>6665267</v>
+        <v>6665288</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1678,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131260641</v>
+        <v>131256730</v>
       </c>
       <c r="B11" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1721,39 +1721,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488859</v>
+        <v>488689</v>
       </c>
       <c r="R11" t="n">
-        <v>6665292</v>
+        <v>6665231</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1785,7 +1780,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,12 +1790,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131257290</v>
+        <v>131257520</v>
       </c>
       <c r="B12" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,39 +1833,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488842</v>
+        <v>488939</v>
       </c>
       <c r="R12" t="n">
-        <v>6665224</v>
+        <v>6665149</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1902,7 +1892,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,12 +1902,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,7 +1934,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131256673</v>
+        <v>131260641</v>
       </c>
       <c r="B13" t="n">
         <v>57888</v>
@@ -1984,10 +1974,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488652</v>
+        <v>488859</v>
       </c>
       <c r="R13" t="n">
-        <v>6665282</v>
+        <v>6665292</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2019,7 +2009,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2029,12 +2019,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,10 +2051,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131256730</v>
+        <v>131257290</v>
       </c>
       <c r="B14" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2072,34 +2062,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488689</v>
+        <v>488842</v>
       </c>
       <c r="R14" t="n">
-        <v>6665231</v>
+        <v>6665224</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2131,7 +2126,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2141,12 +2136,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,10 +2168,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131257520</v>
+        <v>131256673</v>
       </c>
       <c r="B15" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2184,34 +2179,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488939</v>
+        <v>488652</v>
       </c>
       <c r="R15" t="n">
-        <v>6665149</v>
+        <v>6665282</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -4073,10 +4073,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131257659</v>
+        <v>131258537</v>
       </c>
       <c r="B32" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4084,39 +4084,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488901</v>
+        <v>488726</v>
       </c>
       <c r="R32" t="n">
-        <v>6665222</v>
+        <v>6665209</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4148,7 +4143,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4158,12 +4153,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4190,7 +4185,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131258537</v>
+        <v>131255108</v>
       </c>
       <c r="B33" t="n">
         <v>79250</v>
@@ -4225,10 +4220,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488726</v>
+        <v>488978</v>
       </c>
       <c r="R33" t="n">
-        <v>6665209</v>
+        <v>6665417</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4260,7 +4255,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4270,12 +4265,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4302,10 +4297,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131255108</v>
+        <v>131257659</v>
       </c>
       <c r="B34" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4313,34 +4308,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488978</v>
+        <v>488901</v>
       </c>
       <c r="R34" t="n">
-        <v>6665417</v>
+        <v>6665222</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 11705-2024 artfynd.xlsx
+++ b/artfynd/A 11705-2024 artfynd.xlsx
@@ -1027,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131257424</v>
+        <v>131256691</v>
       </c>
       <c r="B5" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,34 +1038,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488876</v>
+        <v>488667</v>
       </c>
       <c r="R5" t="n">
-        <v>6665177</v>
+        <v>6665262</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1107,12 +1112,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131255793</v>
+        <v>131260583</v>
       </c>
       <c r="B6" t="n">
-        <v>91838</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1150,30 +1155,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488817</v>
+        <v>488834</v>
       </c>
       <c r="R6" t="n">
-        <v>6665110</v>
+        <v>6665228</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,7 +1219,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1215,12 +1229,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131256691</v>
+        <v>131257424</v>
       </c>
       <c r="B7" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,39 +1272,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488667</v>
+        <v>488876</v>
       </c>
       <c r="R7" t="n">
-        <v>6665262</v>
+        <v>6665177</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1322,7 +1331,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,12 +1341,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,10 +1373,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131260583</v>
+        <v>131255793</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>91838</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,39 +1384,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488834</v>
+        <v>488817</v>
       </c>
       <c r="R8" t="n">
-        <v>6665228</v>
+        <v>6665110</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 11705-2024 artfynd.xlsx
+++ b/artfynd/A 11705-2024 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>131257487</v>
       </c>
       <c r="B3" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131257646</v>
       </c>
       <c r="B4" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>131256691</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>131260583</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>131257424</v>
       </c>
       <c r="B7" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>131255793</v>
       </c>
       <c r="B8" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131256423</v>
+        <v>131257188</v>
       </c>
       <c r="B9" t="n">
-        <v>57885</v>
+        <v>91841</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,51 +1492,33 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488671</v>
+        <v>488804</v>
       </c>
       <c r="R9" t="n">
-        <v>6665267</v>
+        <v>6665288</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1565,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1575,7 +1557,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1602,10 +1589,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131257188</v>
+        <v>131256423</v>
       </c>
       <c r="B10" t="n">
-        <v>91838</v>
+        <v>57888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,33 +1600,51 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488804</v>
+        <v>488671</v>
       </c>
       <c r="R10" t="n">
-        <v>6665288</v>
+        <v>6665267</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1668,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,12 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131256730</v>
+        <v>131260641</v>
       </c>
       <c r="B11" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1721,34 +1721,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488689</v>
+        <v>488859</v>
       </c>
       <c r="R11" t="n">
-        <v>6665231</v>
+        <v>6665292</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1780,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1790,12 +1795,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131257520</v>
+        <v>131257290</v>
       </c>
       <c r="B12" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1833,34 +1838,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488939</v>
+        <v>488842</v>
       </c>
       <c r="R12" t="n">
-        <v>6665149</v>
+        <v>6665224</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1892,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1902,12 +1912,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,10 +1944,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131260641</v>
+        <v>131256673</v>
       </c>
       <c r="B13" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1974,10 +1984,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488859</v>
+        <v>488652</v>
       </c>
       <c r="R13" t="n">
-        <v>6665292</v>
+        <v>6665282</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2009,7 +2019,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2019,12 +2029,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,10 +2061,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131257290</v>
+        <v>131256730</v>
       </c>
       <c r="B14" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2062,39 +2072,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488842</v>
+        <v>488689</v>
       </c>
       <c r="R14" t="n">
-        <v>6665224</v>
+        <v>6665231</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2126,7 +2131,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2136,12 +2141,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,10 +2173,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131256673</v>
+        <v>131257520</v>
       </c>
       <c r="B15" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2179,39 +2184,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488652</v>
+        <v>488939</v>
       </c>
       <c r="R15" t="n">
-        <v>6665282</v>
+        <v>6665149</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2288,7 +2288,7 @@
         <v>131255096</v>
       </c>
       <c r="B16" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>131257479</v>
       </c>
       <c r="B17" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>131256750</v>
       </c>
       <c r="B18" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>131256401</v>
       </c>
       <c r="B19" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>131256403</v>
       </c>
       <c r="B20" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>131257637</v>
       </c>
       <c r="B21" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>131255771</v>
       </c>
       <c r="B22" t="n">
-        <v>81235</v>
+        <v>81238</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>131257316</v>
       </c>
       <c r="B23" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>131257642</v>
       </c>
       <c r="B24" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>131257045</v>
       </c>
       <c r="B25" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>131257650</v>
       </c>
       <c r="B26" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>131257544</v>
       </c>
       <c r="B27" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3620,10 +3620,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131256649</v>
+        <v>131257239</v>
       </c>
       <c r="B28" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3631,34 +3631,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488685</v>
+        <v>488852</v>
       </c>
       <c r="R28" t="n">
-        <v>6665288</v>
+        <v>6665286</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3690,7 +3695,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3700,12 +3705,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Barkfläk, hagelsalva.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3732,10 +3737,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131255910</v>
+        <v>131256649</v>
       </c>
       <c r="B29" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3767,10 +3772,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488763</v>
+        <v>488685</v>
       </c>
       <c r="R29" t="n">
-        <v>6665157</v>
+        <v>6665288</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3802,7 +3807,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3812,12 +3817,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Tall.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3844,10 +3849,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131258531</v>
+        <v>131255910</v>
       </c>
       <c r="B30" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3879,10 +3884,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488725</v>
+        <v>488763</v>
       </c>
       <c r="R30" t="n">
-        <v>6665212</v>
+        <v>6665157</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3914,7 +3919,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3924,12 +3929,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Tall.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3956,10 +3961,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131257239</v>
+        <v>131258531</v>
       </c>
       <c r="B31" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3967,39 +3972,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488852</v>
+        <v>488725</v>
       </c>
       <c r="R31" t="n">
-        <v>6665286</v>
+        <v>6665212</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4041,12 +4041,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Barkfläk, hagelsalva.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4073,10 +4073,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131258537</v>
+        <v>131257659</v>
       </c>
       <c r="B32" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4084,34 +4084,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488726</v>
+        <v>488901</v>
       </c>
       <c r="R32" t="n">
-        <v>6665209</v>
+        <v>6665222</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4143,7 +4148,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4153,12 +4158,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4185,10 +4190,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131255108</v>
+        <v>131258537</v>
       </c>
       <c r="B33" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4220,10 +4225,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488978</v>
+        <v>488726</v>
       </c>
       <c r="R33" t="n">
-        <v>6665417</v>
+        <v>6665209</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4255,7 +4260,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4265,12 +4270,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4297,10 +4302,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131257659</v>
+        <v>131255108</v>
       </c>
       <c r="B34" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4308,39 +4313,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488901</v>
+        <v>488978</v>
       </c>
       <c r="R34" t="n">
-        <v>6665222</v>
+        <v>6665417</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4417,7 +4417,7 @@
         <v>131257913</v>
       </c>
       <c r="B35" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>131257385</v>
       </c>
       <c r="B36" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>131260531</v>
       </c>
       <c r="B37" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>131256459</v>
       </c>
       <c r="B38" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>131257731</v>
       </c>
       <c r="B39" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>131257440</v>
       </c>
       <c r="B40" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5087,10 +5087,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131257343</v>
+        <v>131257035</v>
       </c>
       <c r="B41" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5098,39 +5098,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488872</v>
+        <v>488760</v>
       </c>
       <c r="R41" t="n">
-        <v>6665191</v>
+        <v>6665301</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5162,7 +5157,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5172,12 +5167,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5204,10 +5199,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131257035</v>
+        <v>131257343</v>
       </c>
       <c r="B42" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5215,34 +5210,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488760</v>
+        <v>488872</v>
       </c>
       <c r="R42" t="n">
-        <v>6665301</v>
+        <v>6665191</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5319,7 +5319,7 @@
         <v>131273946</v>
       </c>
       <c r="B43" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>131273991</v>
       </c>
       <c r="B44" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>131273940</v>
       </c>
       <c r="B45" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 11705-2024 artfynd.xlsx
+++ b/artfynd/A 11705-2024 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>131257487</v>
       </c>
       <c r="B3" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131257646</v>
       </c>
       <c r="B4" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>131256691</v>
       </c>
       <c r="B5" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>131260583</v>
       </c>
       <c r="B6" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>131257424</v>
       </c>
       <c r="B7" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>131255793</v>
       </c>
       <c r="B8" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>131257188</v>
       </c>
       <c r="B9" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>131256423</v>
       </c>
       <c r="B10" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131260641</v>
+        <v>131257520</v>
       </c>
       <c r="B11" t="n">
-        <v>57891</v>
+        <v>79254</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1721,39 +1721,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488859</v>
+        <v>488939</v>
       </c>
       <c r="R11" t="n">
-        <v>6665292</v>
+        <v>6665149</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1785,7 +1780,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,12 +1790,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131257290</v>
+        <v>131256730</v>
       </c>
       <c r="B12" t="n">
-        <v>57891</v>
+        <v>79254</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,39 +1833,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488842</v>
+        <v>488689</v>
       </c>
       <c r="R12" t="n">
-        <v>6665224</v>
+        <v>6665231</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1902,7 +1892,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,12 +1902,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,10 +1934,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131256673</v>
+        <v>131260641</v>
       </c>
       <c r="B13" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1984,10 +1974,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488652</v>
+        <v>488859</v>
       </c>
       <c r="R13" t="n">
-        <v>6665282</v>
+        <v>6665292</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2019,7 +2009,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2029,12 +2019,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,10 +2051,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131256730</v>
+        <v>131257290</v>
       </c>
       <c r="B14" t="n">
-        <v>79253</v>
+        <v>57892</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2072,34 +2062,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488689</v>
+        <v>488842</v>
       </c>
       <c r="R14" t="n">
-        <v>6665231</v>
+        <v>6665224</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2131,7 +2126,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2141,12 +2136,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,10 +2168,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131257520</v>
+        <v>131256673</v>
       </c>
       <c r="B15" t="n">
-        <v>79253</v>
+        <v>57892</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2184,34 +2179,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488939</v>
+        <v>488652</v>
       </c>
       <c r="R15" t="n">
-        <v>6665149</v>
+        <v>6665282</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2288,7 +2288,7 @@
         <v>131255096</v>
       </c>
       <c r="B16" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>131257479</v>
       </c>
       <c r="B17" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>131256750</v>
       </c>
       <c r="B18" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>131256401</v>
       </c>
       <c r="B19" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>131256403</v>
       </c>
       <c r="B20" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>131257637</v>
       </c>
       <c r="B21" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2953,10 +2953,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131255771</v>
+        <v>131257316</v>
       </c>
       <c r="B22" t="n">
-        <v>81238</v>
+        <v>79254</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2964,21 +2964,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488818</v>
+        <v>488852</v>
       </c>
       <c r="R22" t="n">
-        <v>6665110</v>
+        <v>6665209</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3033,7 +3033,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3060,10 +3065,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131257316</v>
+        <v>131255771</v>
       </c>
       <c r="B23" t="n">
-        <v>79253</v>
+        <v>81239</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3071,21 +3076,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3095,10 +3100,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488852</v>
+        <v>488818</v>
       </c>
       <c r="R23" t="n">
-        <v>6665209</v>
+        <v>6665110</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3130,7 +3135,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3140,12 +3145,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3175,7 +3175,7 @@
         <v>131257642</v>
       </c>
       <c r="B24" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>131257045</v>
       </c>
       <c r="B25" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>131257650</v>
       </c>
       <c r="B26" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>131257544</v>
       </c>
       <c r="B27" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3620,10 +3620,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131257239</v>
+        <v>131255910</v>
       </c>
       <c r="B28" t="n">
-        <v>57891</v>
+        <v>79254</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3631,39 +3631,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488852</v>
+        <v>488763</v>
       </c>
       <c r="R28" t="n">
-        <v>6665286</v>
+        <v>6665157</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3695,7 +3690,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3705,12 +3700,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Barkfläk, hagelsalva.</t>
+          <t>Tall.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3737,10 +3732,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131256649</v>
+        <v>131258531</v>
       </c>
       <c r="B29" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3772,10 +3767,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488685</v>
+        <v>488725</v>
       </c>
       <c r="R29" t="n">
-        <v>6665288</v>
+        <v>6665212</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3807,7 +3802,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3817,12 +3812,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3849,10 +3844,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131255910</v>
+        <v>131256649</v>
       </c>
       <c r="B30" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3884,10 +3879,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488763</v>
+        <v>488685</v>
       </c>
       <c r="R30" t="n">
-        <v>6665157</v>
+        <v>6665288</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3919,7 +3914,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3929,12 +3924,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Tall.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3961,10 +3956,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131258531</v>
+        <v>131257239</v>
       </c>
       <c r="B31" t="n">
-        <v>79253</v>
+        <v>57892</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3972,34 +3967,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488725</v>
+        <v>488852</v>
       </c>
       <c r="R31" t="n">
-        <v>6665212</v>
+        <v>6665286</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4041,12 +4041,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Barkfläk, hagelsalva.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4073,10 +4073,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131257659</v>
+        <v>131258537</v>
       </c>
       <c r="B32" t="n">
-        <v>57891</v>
+        <v>79254</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4084,39 +4084,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488901</v>
+        <v>488726</v>
       </c>
       <c r="R32" t="n">
-        <v>6665222</v>
+        <v>6665209</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4148,7 +4143,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4158,12 +4153,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4190,10 +4185,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131258537</v>
+        <v>131255108</v>
       </c>
       <c r="B33" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4225,10 +4220,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488726</v>
+        <v>488978</v>
       </c>
       <c r="R33" t="n">
-        <v>6665209</v>
+        <v>6665417</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4260,7 +4255,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4270,12 +4265,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4302,10 +4297,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131255108</v>
+        <v>131257659</v>
       </c>
       <c r="B34" t="n">
-        <v>79253</v>
+        <v>57892</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4313,34 +4308,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488978</v>
+        <v>488901</v>
       </c>
       <c r="R34" t="n">
-        <v>6665417</v>
+        <v>6665222</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4417,7 +4417,7 @@
         <v>131257913</v>
       </c>
       <c r="B35" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>131257385</v>
       </c>
       <c r="B36" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>131260531</v>
       </c>
       <c r="B37" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>131256459</v>
       </c>
       <c r="B38" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>131257731</v>
       </c>
       <c r="B39" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>131257440</v>
       </c>
       <c r="B40" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5087,10 +5087,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131257035</v>
+        <v>131257343</v>
       </c>
       <c r="B41" t="n">
-        <v>79253</v>
+        <v>57892</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5098,34 +5098,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488760</v>
+        <v>488872</v>
       </c>
       <c r="R41" t="n">
-        <v>6665301</v>
+        <v>6665191</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5157,7 +5162,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5167,12 +5172,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5199,10 +5204,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131257343</v>
+        <v>131257035</v>
       </c>
       <c r="B42" t="n">
-        <v>57891</v>
+        <v>79254</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5210,39 +5215,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488872</v>
+        <v>488760</v>
       </c>
       <c r="R42" t="n">
-        <v>6665191</v>
+        <v>6665301</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5319,7 +5319,7 @@
         <v>131273946</v>
       </c>
       <c r="B43" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>131273991</v>
       </c>
       <c r="B44" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>131273940</v>
       </c>
       <c r="B45" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 11705-2024 artfynd.xlsx
+++ b/artfynd/A 11705-2024 artfynd.xlsx
@@ -3620,7 +3620,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131255910</v>
+        <v>131256649</v>
       </c>
       <c r="B28" t="n">
         <v>79254</v>
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488763</v>
+        <v>488685</v>
       </c>
       <c r="R28" t="n">
-        <v>6665157</v>
+        <v>6665288</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Tall.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3732,7 +3732,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131258531</v>
+        <v>131255910</v>
       </c>
       <c r="B29" t="n">
         <v>79254</v>
@@ -3767,10 +3767,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488725</v>
+        <v>488763</v>
       </c>
       <c r="R29" t="n">
-        <v>6665212</v>
+        <v>6665157</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Tall.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3844,7 +3844,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131256649</v>
+        <v>131258531</v>
       </c>
       <c r="B30" t="n">
         <v>79254</v>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488685</v>
+        <v>488725</v>
       </c>
       <c r="R30" t="n">
-        <v>6665288</v>
+        <v>6665212</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3924,12 +3924,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 11705-2024 artfynd.xlsx
+++ b/artfynd/A 11705-2024 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>131257487</v>
       </c>
       <c r="B3" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131257646</v>
       </c>
       <c r="B4" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131256691</v>
+        <v>131255793</v>
       </c>
       <c r="B5" t="n">
-        <v>57892</v>
+        <v>91848</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,39 +1038,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488667</v>
+        <v>488817</v>
       </c>
       <c r="R5" t="n">
-        <v>6665262</v>
+        <v>6665110</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,12 +1103,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131260583</v>
+        <v>131257424</v>
       </c>
       <c r="B6" t="n">
-        <v>57892</v>
+        <v>79260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,39 +1146,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488834</v>
+        <v>488876</v>
       </c>
       <c r="R6" t="n">
-        <v>6665228</v>
+        <v>6665177</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1219,7 +1205,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1229,12 +1215,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131257424</v>
+        <v>131256691</v>
       </c>
       <c r="B7" t="n">
-        <v>79254</v>
+        <v>57898</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,34 +1258,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488876</v>
+        <v>488667</v>
       </c>
       <c r="R7" t="n">
-        <v>6665177</v>
+        <v>6665262</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1331,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1341,12 +1332,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131255793</v>
+        <v>131260583</v>
       </c>
       <c r="B8" t="n">
-        <v>91842</v>
+        <v>57898</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1384,30 +1375,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488817</v>
+        <v>488834</v>
       </c>
       <c r="R8" t="n">
-        <v>6665110</v>
+        <v>6665228</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131257188</v>
+        <v>131256423</v>
       </c>
       <c r="B9" t="n">
-        <v>91842</v>
+        <v>57895</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,33 +1492,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488804</v>
+        <v>488671</v>
       </c>
       <c r="R9" t="n">
-        <v>6665288</v>
+        <v>6665267</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1547,7 +1565,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,12 +1575,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,10 +1602,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131256423</v>
+        <v>131257188</v>
       </c>
       <c r="B10" t="n">
-        <v>57889</v>
+        <v>91848</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,51 +1613,33 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488671</v>
+        <v>488804</v>
       </c>
       <c r="R10" t="n">
-        <v>6665267</v>
+        <v>6665288</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1678,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131257520</v>
+        <v>131256730</v>
       </c>
       <c r="B11" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488939</v>
+        <v>488689</v>
       </c>
       <c r="R11" t="n">
-        <v>6665149</v>
+        <v>6665231</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131256730</v>
+        <v>131257520</v>
       </c>
       <c r="B12" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488689</v>
+        <v>488939</v>
       </c>
       <c r="R12" t="n">
-        <v>6665231</v>
+        <v>6665149</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,7 +1937,7 @@
         <v>131260641</v>
       </c>
       <c r="B13" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>131257290</v>
       </c>
       <c r="B14" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>131256673</v>
       </c>
       <c r="B15" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>131255096</v>
       </c>
       <c r="B16" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>131257479</v>
       </c>
       <c r="B17" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>131256750</v>
       </c>
       <c r="B18" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>131256401</v>
       </c>
       <c r="B19" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>131256403</v>
       </c>
       <c r="B20" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>131257637</v>
       </c>
       <c r="B21" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2953,10 +2953,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131257316</v>
+        <v>131255771</v>
       </c>
       <c r="B22" t="n">
-        <v>79254</v>
+        <v>81245</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2964,21 +2964,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488852</v>
+        <v>488818</v>
       </c>
       <c r="R22" t="n">
-        <v>6665209</v>
+        <v>6665110</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3033,12 +3033,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3065,10 +3060,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131255771</v>
+        <v>131257316</v>
       </c>
       <c r="B23" t="n">
-        <v>81239</v>
+        <v>79260</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3076,21 +3071,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3100,10 +3095,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488818</v>
+        <v>488852</v>
       </c>
       <c r="R23" t="n">
-        <v>6665110</v>
+        <v>6665209</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3135,7 +3130,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3145,7 +3140,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3175,7 +3175,7 @@
         <v>131257642</v>
       </c>
       <c r="B24" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>131257045</v>
       </c>
       <c r="B25" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>131257650</v>
       </c>
       <c r="B26" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>131257544</v>
       </c>
       <c r="B27" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>131256649</v>
       </c>
       <c r="B28" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>131255910</v>
       </c>
       <c r="B29" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>131258531</v>
       </c>
       <c r="B30" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>131257239</v>
       </c>
       <c r="B31" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4073,10 +4073,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131258537</v>
+        <v>131257659</v>
       </c>
       <c r="B32" t="n">
-        <v>79254</v>
+        <v>57898</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4084,34 +4084,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488726</v>
+        <v>488901</v>
       </c>
       <c r="R32" t="n">
-        <v>6665209</v>
+        <v>6665222</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4143,7 +4148,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4153,12 +4158,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4185,10 +4190,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131255108</v>
+        <v>131258537</v>
       </c>
       <c r="B33" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4220,10 +4225,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488978</v>
+        <v>488726</v>
       </c>
       <c r="R33" t="n">
-        <v>6665417</v>
+        <v>6665209</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4255,7 +4260,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4265,12 +4270,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4297,10 +4302,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131257659</v>
+        <v>131255108</v>
       </c>
       <c r="B34" t="n">
-        <v>57892</v>
+        <v>79260</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4308,39 +4313,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488901</v>
+        <v>488978</v>
       </c>
       <c r="R34" t="n">
-        <v>6665222</v>
+        <v>6665417</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4417,7 +4417,7 @@
         <v>131257913</v>
       </c>
       <c r="B35" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>131257385</v>
       </c>
       <c r="B36" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>131260531</v>
       </c>
       <c r="B37" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>131256459</v>
       </c>
       <c r="B38" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>131257731</v>
       </c>
       <c r="B39" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>131257440</v>
       </c>
       <c r="B40" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5087,10 +5087,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131257343</v>
+        <v>131257035</v>
       </c>
       <c r="B41" t="n">
-        <v>57892</v>
+        <v>79260</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5098,39 +5098,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488872</v>
+        <v>488760</v>
       </c>
       <c r="R41" t="n">
-        <v>6665191</v>
+        <v>6665301</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5162,7 +5157,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5172,12 +5167,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5204,10 +5199,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131257035</v>
+        <v>131257343</v>
       </c>
       <c r="B42" t="n">
-        <v>79254</v>
+        <v>57898</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5215,34 +5210,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488760</v>
+        <v>488872</v>
       </c>
       <c r="R42" t="n">
-        <v>6665301</v>
+        <v>6665191</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5319,7 +5319,7 @@
         <v>131273946</v>
       </c>
       <c r="B43" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>131273991</v>
       </c>
       <c r="B44" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>131273940</v>
       </c>
       <c r="B45" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 11705-2024 artfynd.xlsx
+++ b/artfynd/A 11705-2024 artfynd.xlsx
@@ -1481,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131256423</v>
+        <v>131257188</v>
       </c>
       <c r="B9" t="n">
-        <v>57895</v>
+        <v>91848</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,51 +1492,33 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488671</v>
+        <v>488804</v>
       </c>
       <c r="R9" t="n">
-        <v>6665267</v>
+        <v>6665288</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1565,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1575,7 +1557,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1602,10 +1589,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131257188</v>
+        <v>131256423</v>
       </c>
       <c r="B10" t="n">
-        <v>91848</v>
+        <v>57895</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,33 +1600,51 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488804</v>
+        <v>488671</v>
       </c>
       <c r="R10" t="n">
-        <v>6665288</v>
+        <v>6665267</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1668,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,12 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 11705-2024 artfynd.xlsx
+++ b/artfynd/A 11705-2024 artfynd.xlsx
@@ -1027,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131255793</v>
+        <v>131257424</v>
       </c>
       <c r="B5" t="n">
-        <v>91848</v>
+        <v>79260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,19 +1038,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488817</v>
+        <v>488876</v>
       </c>
       <c r="R5" t="n">
-        <v>6665110</v>
+        <v>6665177</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1093,7 +1097,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,12 +1107,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131257424</v>
+        <v>131255793</v>
       </c>
       <c r="B6" t="n">
-        <v>79260</v>
+        <v>91848</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1146,23 +1150,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488876</v>
+        <v>488817</v>
       </c>
       <c r="R6" t="n">
-        <v>6665177</v>
+        <v>6665110</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1215,12 +1215,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -4073,10 +4073,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131257659</v>
+        <v>131258537</v>
       </c>
       <c r="B32" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4084,39 +4084,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488901</v>
+        <v>488726</v>
       </c>
       <c r="R32" t="n">
-        <v>6665222</v>
+        <v>6665209</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4148,7 +4143,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4158,12 +4153,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4190,7 +4185,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131258537</v>
+        <v>131255108</v>
       </c>
       <c r="B33" t="n">
         <v>79260</v>
@@ -4225,10 +4220,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488726</v>
+        <v>488978</v>
       </c>
       <c r="R33" t="n">
-        <v>6665209</v>
+        <v>6665417</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4260,7 +4255,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4270,12 +4265,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4302,10 +4297,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131255108</v>
+        <v>131257659</v>
       </c>
       <c r="B34" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4313,34 +4308,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488978</v>
+        <v>488901</v>
       </c>
       <c r="R34" t="n">
-        <v>6665417</v>
+        <v>6665222</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4526,10 +4526,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131257385</v>
+        <v>131256459</v>
       </c>
       <c r="B36" t="n">
-        <v>91848</v>
+        <v>57895</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4537,30 +4537,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488876</v>
+        <v>488669</v>
       </c>
       <c r="R36" t="n">
-        <v>6665194</v>
+        <v>6665268</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4592,7 +4601,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4602,12 +4611,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Lågstubbe.</t>
+          <t>Färska och äldre hack.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4634,10 +4643,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131260531</v>
+        <v>131257385</v>
       </c>
       <c r="B37" t="n">
-        <v>79260</v>
+        <v>91848</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4645,23 +4654,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4669,10 +4674,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488786</v>
+        <v>488876</v>
       </c>
       <c r="R37" t="n">
-        <v>6665188</v>
+        <v>6665194</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4704,7 +4709,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4714,12 +4719,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Lågstubbe.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4746,10 +4751,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131256459</v>
+        <v>131260531</v>
       </c>
       <c r="B38" t="n">
-        <v>57895</v>
+        <v>79260</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4757,39 +4762,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488669</v>
+        <v>488786</v>
       </c>
       <c r="R38" t="n">
-        <v>6665268</v>
+        <v>6665188</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska och äldre hack.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 11705-2024 artfynd.xlsx
+++ b/artfynd/A 11705-2024 artfynd.xlsx
@@ -4526,10 +4526,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131256459</v>
+        <v>131257385</v>
       </c>
       <c r="B36" t="n">
-        <v>57895</v>
+        <v>91848</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4537,39 +4537,30 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488669</v>
+        <v>488876</v>
       </c>
       <c r="R36" t="n">
-        <v>6665268</v>
+        <v>6665194</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4601,7 +4592,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4611,12 +4602,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska och äldre hack.</t>
+          <t>Lågstubbe.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4643,10 +4634,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131257385</v>
+        <v>131260531</v>
       </c>
       <c r="B37" t="n">
-        <v>91848</v>
+        <v>79260</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4654,19 +4645,23 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4674,10 +4669,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488876</v>
+        <v>488786</v>
       </c>
       <c r="R37" t="n">
-        <v>6665194</v>
+        <v>6665188</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4709,7 +4704,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4719,12 +4714,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Lågstubbe.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4751,10 +4746,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131260531</v>
+        <v>131256459</v>
       </c>
       <c r="B38" t="n">
-        <v>79260</v>
+        <v>57895</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4762,34 +4757,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488786</v>
+        <v>488669</v>
       </c>
       <c r="R38" t="n">
-        <v>6665188</v>
+        <v>6665268</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Färska och äldre hack.</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 11705-2024 artfynd.xlsx
+++ b/artfynd/A 11705-2024 artfynd.xlsx
@@ -1027,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131257424</v>
+        <v>131255793</v>
       </c>
       <c r="B5" t="n">
-        <v>79260</v>
+        <v>91848</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,23 +1038,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1062,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488876</v>
+        <v>488817</v>
       </c>
       <c r="R5" t="n">
-        <v>6665177</v>
+        <v>6665110</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1107,12 +1103,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131255793</v>
+        <v>131257424</v>
       </c>
       <c r="B6" t="n">
-        <v>91848</v>
+        <v>79260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1150,19 +1146,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488817</v>
+        <v>488876</v>
       </c>
       <c r="R6" t="n">
-        <v>6665110</v>
+        <v>6665177</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1215,12 +1215,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1481,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131257188</v>
+        <v>131256423</v>
       </c>
       <c r="B9" t="n">
-        <v>91848</v>
+        <v>57895</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,33 +1492,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488804</v>
+        <v>488671</v>
       </c>
       <c r="R9" t="n">
-        <v>6665288</v>
+        <v>6665267</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1547,7 +1565,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,12 +1575,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,10 +1602,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131256423</v>
+        <v>131257188</v>
       </c>
       <c r="B10" t="n">
-        <v>57895</v>
+        <v>91848</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,51 +1613,33 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488671</v>
+        <v>488804</v>
       </c>
       <c r="R10" t="n">
-        <v>6665267</v>
+        <v>6665288</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1678,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131255096</v>
+        <v>131257479</v>
       </c>
       <c r="B16" t="n">
-        <v>79260</v>
+        <v>91848</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2296,23 +2296,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2320,10 +2316,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488961</v>
+        <v>488908</v>
       </c>
       <c r="R16" t="n">
-        <v>6665423</v>
+        <v>6665154</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2355,7 +2351,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2365,12 +2361,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Stambrott. Hängande låga.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2397,10 +2393,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131257479</v>
+        <v>131256750</v>
       </c>
       <c r="B17" t="n">
-        <v>91848</v>
+        <v>79260</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2408,19 +2404,23 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488908</v>
+        <v>488704</v>
       </c>
       <c r="R17" t="n">
-        <v>6665154</v>
+        <v>6665241</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Stambrott. Hängande låga.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2505,7 +2505,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131256750</v>
+        <v>131255096</v>
       </c>
       <c r="B18" t="n">
         <v>79260</v>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488704</v>
+        <v>488961</v>
       </c>
       <c r="R18" t="n">
-        <v>6665241</v>
+        <v>6665423</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2617,7 +2617,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131256401</v>
+        <v>131256403</v>
       </c>
       <c r="B19" t="n">
         <v>79260</v>
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488679</v>
+        <v>488680</v>
       </c>
       <c r="R19" t="n">
-        <v>6665255</v>
+        <v>6665257</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2729,7 +2729,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131256403</v>
+        <v>131256401</v>
       </c>
       <c r="B20" t="n">
         <v>79260</v>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488680</v>
+        <v>488679</v>
       </c>
       <c r="R20" t="n">
-        <v>6665257</v>
+        <v>6665255</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2953,10 +2953,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131255771</v>
+        <v>131257316</v>
       </c>
       <c r="B22" t="n">
-        <v>81245</v>
+        <v>79260</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2964,21 +2964,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488818</v>
+        <v>488852</v>
       </c>
       <c r="R22" t="n">
-        <v>6665110</v>
+        <v>6665209</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3033,7 +3033,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3060,10 +3065,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131257316</v>
+        <v>131255771</v>
       </c>
       <c r="B23" t="n">
-        <v>79260</v>
+        <v>81245</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3071,21 +3076,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3095,10 +3100,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488852</v>
+        <v>488818</v>
       </c>
       <c r="R23" t="n">
-        <v>6665209</v>
+        <v>6665110</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3130,7 +3135,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3140,12 +3145,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3284,7 +3284,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131257045</v>
+        <v>131257650</v>
       </c>
       <c r="B25" t="n">
         <v>79260</v>
@@ -3319,10 +3319,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488760</v>
+        <v>488911</v>
       </c>
       <c r="R25" t="n">
-        <v>6665302</v>
+        <v>6665227</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3396,7 +3396,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131257650</v>
+        <v>131257045</v>
       </c>
       <c r="B26" t="n">
         <v>79260</v>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488911</v>
+        <v>488760</v>
       </c>
       <c r="R26" t="n">
-        <v>6665227</v>
+        <v>6665302</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4526,10 +4526,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131257385</v>
+        <v>131260531</v>
       </c>
       <c r="B36" t="n">
-        <v>91848</v>
+        <v>79260</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4537,19 +4537,23 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4557,10 +4561,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488876</v>
+        <v>488786</v>
       </c>
       <c r="R36" t="n">
-        <v>6665194</v>
+        <v>6665188</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4592,7 +4596,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4602,12 +4606,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Lågstubbe.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4634,10 +4638,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131260531</v>
+        <v>131257385</v>
       </c>
       <c r="B37" t="n">
-        <v>79260</v>
+        <v>91848</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4645,23 +4649,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488786</v>
+        <v>488876</v>
       </c>
       <c r="R37" t="n">
-        <v>6665188</v>
+        <v>6665194</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4714,12 +4714,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Lågstubbe.</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 11705-2024 artfynd.xlsx
+++ b/artfynd/A 11705-2024 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>131257487</v>
       </c>
       <c r="B3" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131257646</v>
       </c>
       <c r="B4" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>131255793</v>
       </c>
       <c r="B5" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131257424</v>
+        <v>131256691</v>
       </c>
       <c r="B6" t="n">
-        <v>79260</v>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1146,34 +1146,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488876</v>
+        <v>488667</v>
       </c>
       <c r="R6" t="n">
-        <v>6665177</v>
+        <v>6665262</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1215,12 +1220,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131256691</v>
+        <v>131260583</v>
       </c>
       <c r="B7" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1283,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1287,10 +1292,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488667</v>
+        <v>488834</v>
       </c>
       <c r="R7" t="n">
-        <v>6665262</v>
+        <v>6665228</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1322,7 +1327,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,12 +1337,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,10 +1369,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131260583</v>
+        <v>131257424</v>
       </c>
       <c r="B8" t="n">
-        <v>57898</v>
+        <v>79261</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,39 +1380,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488834</v>
+        <v>488876</v>
       </c>
       <c r="R8" t="n">
-        <v>6665228</v>
+        <v>6665177</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131256423</v>
+        <v>131257188</v>
       </c>
       <c r="B9" t="n">
-        <v>57895</v>
+        <v>91849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,51 +1492,33 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488671</v>
+        <v>488804</v>
       </c>
       <c r="R9" t="n">
-        <v>6665267</v>
+        <v>6665288</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1565,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1575,7 +1557,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1602,10 +1589,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131257188</v>
+        <v>131256423</v>
       </c>
       <c r="B10" t="n">
-        <v>91848</v>
+        <v>57896</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,33 +1600,51 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488804</v>
+        <v>488671</v>
       </c>
       <c r="R10" t="n">
-        <v>6665288</v>
+        <v>6665267</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1668,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,12 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,7 +1713,7 @@
         <v>131256730</v>
       </c>
       <c r="B11" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>131257520</v>
       </c>
       <c r="B12" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>131260641</v>
       </c>
       <c r="B13" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>131257290</v>
       </c>
       <c r="B14" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>131256673</v>
       </c>
       <c r="B15" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>131257479</v>
       </c>
       <c r="B16" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2393,10 +2393,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131256750</v>
+        <v>131255096</v>
       </c>
       <c r="B17" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488704</v>
+        <v>488961</v>
       </c>
       <c r="R17" t="n">
-        <v>6665241</v>
+        <v>6665423</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2505,10 +2505,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131255096</v>
+        <v>131256750</v>
       </c>
       <c r="B18" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488961</v>
+        <v>488704</v>
       </c>
       <c r="R18" t="n">
-        <v>6665423</v>
+        <v>6665241</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2617,10 +2617,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131256403</v>
+        <v>131256401</v>
       </c>
       <c r="B19" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488680</v>
+        <v>488679</v>
       </c>
       <c r="R19" t="n">
-        <v>6665257</v>
+        <v>6665255</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2729,10 +2729,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131256401</v>
+        <v>131256403</v>
       </c>
       <c r="B20" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488679</v>
+        <v>488680</v>
       </c>
       <c r="R20" t="n">
-        <v>6665255</v>
+        <v>6665257</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2844,7 +2844,7 @@
         <v>131257637</v>
       </c>
       <c r="B21" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2953,10 +2953,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131257316</v>
+        <v>131255771</v>
       </c>
       <c r="B22" t="n">
-        <v>79260</v>
+        <v>81246</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2964,21 +2964,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488852</v>
+        <v>488818</v>
       </c>
       <c r="R22" t="n">
-        <v>6665209</v>
+        <v>6665110</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3033,12 +3033,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3065,10 +3060,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131255771</v>
+        <v>131257316</v>
       </c>
       <c r="B23" t="n">
-        <v>81245</v>
+        <v>79261</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3076,21 +3071,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3100,10 +3095,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488818</v>
+        <v>488852</v>
       </c>
       <c r="R23" t="n">
-        <v>6665110</v>
+        <v>6665209</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3135,7 +3130,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3145,7 +3140,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3175,7 +3175,7 @@
         <v>131257642</v>
       </c>
       <c r="B24" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3284,10 +3284,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131257650</v>
+        <v>131257045</v>
       </c>
       <c r="B25" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3319,10 +3319,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488911</v>
+        <v>488760</v>
       </c>
       <c r="R25" t="n">
-        <v>6665227</v>
+        <v>6665302</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3396,10 +3396,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131257045</v>
+        <v>131257650</v>
       </c>
       <c r="B26" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488760</v>
+        <v>488911</v>
       </c>
       <c r="R26" t="n">
-        <v>6665302</v>
+        <v>6665227</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3511,7 +3511,7 @@
         <v>131257544</v>
       </c>
       <c r="B27" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>131256649</v>
       </c>
       <c r="B28" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>131255910</v>
       </c>
       <c r="B29" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>131258531</v>
       </c>
       <c r="B30" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>131257239</v>
       </c>
       <c r="B31" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4073,10 +4073,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131258537</v>
+        <v>131257659</v>
       </c>
       <c r="B32" t="n">
-        <v>79260</v>
+        <v>57899</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4084,34 +4084,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488726</v>
+        <v>488901</v>
       </c>
       <c r="R32" t="n">
-        <v>6665209</v>
+        <v>6665222</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4143,7 +4148,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4153,12 +4158,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4185,10 +4190,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131255108</v>
+        <v>131258537</v>
       </c>
       <c r="B33" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4220,10 +4225,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488978</v>
+        <v>488726</v>
       </c>
       <c r="R33" t="n">
-        <v>6665417</v>
+        <v>6665209</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4255,7 +4260,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4265,12 +4270,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4297,10 +4302,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131257659</v>
+        <v>131255108</v>
       </c>
       <c r="B34" t="n">
-        <v>57898</v>
+        <v>79261</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4308,39 +4313,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488901</v>
+        <v>488978</v>
       </c>
       <c r="R34" t="n">
-        <v>6665222</v>
+        <v>6665417</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4417,7 +4417,7 @@
         <v>131257913</v>
       </c>
       <c r="B35" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131260531</v>
+        <v>131256459</v>
       </c>
       <c r="B36" t="n">
-        <v>79260</v>
+        <v>57896</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4537,34 +4537,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488786</v>
+        <v>488669</v>
       </c>
       <c r="R36" t="n">
-        <v>6665188</v>
+        <v>6665268</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4596,7 +4601,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4606,12 +4611,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Färska och äldre hack.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4641,7 +4646,7 @@
         <v>131257385</v>
       </c>
       <c r="B37" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,10 +4751,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131256459</v>
+        <v>131260531</v>
       </c>
       <c r="B38" t="n">
-        <v>57895</v>
+        <v>79261</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4757,39 +4762,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488669</v>
+        <v>488786</v>
       </c>
       <c r="R38" t="n">
-        <v>6665268</v>
+        <v>6665188</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska och äldre hack.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4866,7 +4866,7 @@
         <v>131257731</v>
       </c>
       <c r="B39" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>131257440</v>
       </c>
       <c r="B40" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>131257035</v>
       </c>
       <c r="B41" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>131257343</v>
       </c>
       <c r="B42" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>131273946</v>
       </c>
       <c r="B43" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>131273991</v>
       </c>
       <c r="B44" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>131273940</v>
       </c>
       <c r="B45" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 11705-2024 artfynd.xlsx
+++ b/artfynd/A 11705-2024 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>131257487</v>
       </c>
       <c r="B3" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131257646</v>
       </c>
       <c r="B4" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131255793</v>
+        <v>131256691</v>
       </c>
       <c r="B5" t="n">
-        <v>91849</v>
+        <v>57902</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,30 +1038,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488817</v>
+        <v>488667</v>
       </c>
       <c r="R5" t="n">
-        <v>6665110</v>
+        <v>6665262</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1093,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,12 +1112,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131256691</v>
+        <v>131260583</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,7 +1175,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1175,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488667</v>
+        <v>488834</v>
       </c>
       <c r="R6" t="n">
-        <v>6665262</v>
+        <v>6665228</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,7 +1219,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1220,12 +1229,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131260583</v>
+        <v>131257424</v>
       </c>
       <c r="B7" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1263,39 +1272,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488834</v>
+        <v>488876</v>
       </c>
       <c r="R7" t="n">
-        <v>6665228</v>
+        <v>6665177</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1327,7 +1331,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1337,12 +1341,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,10 +1373,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131257424</v>
+        <v>131255793</v>
       </c>
       <c r="B8" t="n">
-        <v>79261</v>
+        <v>91852</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,23 +1384,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488876</v>
+        <v>488817</v>
       </c>
       <c r="R8" t="n">
-        <v>6665177</v>
+        <v>6665110</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131257188</v>
+        <v>131256423</v>
       </c>
       <c r="B9" t="n">
-        <v>91849</v>
+        <v>57899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,33 +1492,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488804</v>
+        <v>488671</v>
       </c>
       <c r="R9" t="n">
-        <v>6665288</v>
+        <v>6665267</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1547,7 +1565,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,12 +1575,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,10 +1602,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131256423</v>
+        <v>131257188</v>
       </c>
       <c r="B10" t="n">
-        <v>57896</v>
+        <v>91852</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,51 +1613,33 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488671</v>
+        <v>488804</v>
       </c>
       <c r="R10" t="n">
-        <v>6665267</v>
+        <v>6665288</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1678,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131256730</v>
+        <v>131260641</v>
       </c>
       <c r="B11" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1721,34 +1721,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488689</v>
+        <v>488859</v>
       </c>
       <c r="R11" t="n">
-        <v>6665231</v>
+        <v>6665292</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1780,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1790,12 +1795,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131257520</v>
+        <v>131257290</v>
       </c>
       <c r="B12" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1833,34 +1838,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488939</v>
+        <v>488842</v>
       </c>
       <c r="R12" t="n">
-        <v>6665149</v>
+        <v>6665224</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1892,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1902,12 +1912,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,10 +1944,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131260641</v>
+        <v>131256673</v>
       </c>
       <c r="B13" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1974,10 +1984,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488859</v>
+        <v>488652</v>
       </c>
       <c r="R13" t="n">
-        <v>6665292</v>
+        <v>6665282</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2009,7 +2019,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2019,12 +2029,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,10 +2061,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131257290</v>
+        <v>131256730</v>
       </c>
       <c r="B14" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2062,39 +2072,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488842</v>
+        <v>488689</v>
       </c>
       <c r="R14" t="n">
-        <v>6665224</v>
+        <v>6665231</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2126,7 +2131,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2136,12 +2141,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,10 +2173,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131256673</v>
+        <v>131257520</v>
       </c>
       <c r="B15" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2179,39 +2184,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488652</v>
+        <v>488939</v>
       </c>
       <c r="R15" t="n">
-        <v>6665282</v>
+        <v>6665149</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131257479</v>
+        <v>131255096</v>
       </c>
       <c r="B16" t="n">
-        <v>91849</v>
+        <v>79264</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2296,19 +2296,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2316,10 +2320,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488908</v>
+        <v>488961</v>
       </c>
       <c r="R16" t="n">
-        <v>6665154</v>
+        <v>6665423</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2351,7 +2355,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2361,12 +2365,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Stambrott. Hängande låga.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2393,10 +2397,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131255096</v>
+        <v>131257479</v>
       </c>
       <c r="B17" t="n">
-        <v>79261</v>
+        <v>91852</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2404,23 +2408,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488961</v>
+        <v>488908</v>
       </c>
       <c r="R17" t="n">
-        <v>6665423</v>
+        <v>6665154</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Stambrott. Hängande låga.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2508,7 +2508,7 @@
         <v>131256750</v>
       </c>
       <c r="B18" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>131256401</v>
       </c>
       <c r="B19" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>131256403</v>
       </c>
       <c r="B20" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>131257637</v>
       </c>
       <c r="B21" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2953,10 +2953,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131255771</v>
+        <v>131257316</v>
       </c>
       <c r="B22" t="n">
-        <v>81246</v>
+        <v>79264</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2964,21 +2964,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488818</v>
+        <v>488852</v>
       </c>
       <c r="R22" t="n">
-        <v>6665110</v>
+        <v>6665209</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3033,7 +3033,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3060,10 +3065,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131257316</v>
+        <v>131255771</v>
       </c>
       <c r="B23" t="n">
-        <v>79261</v>
+        <v>81249</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3071,21 +3076,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3095,10 +3100,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488852</v>
+        <v>488818</v>
       </c>
       <c r="R23" t="n">
-        <v>6665209</v>
+        <v>6665110</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3130,7 +3135,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3140,12 +3145,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3175,7 +3175,7 @@
         <v>131257642</v>
       </c>
       <c r="B24" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>131257045</v>
       </c>
       <c r="B25" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>131257650</v>
       </c>
       <c r="B26" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>131257544</v>
       </c>
       <c r="B27" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3620,10 +3620,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131256649</v>
+        <v>131257239</v>
       </c>
       <c r="B28" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3631,34 +3631,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488685</v>
+        <v>488852</v>
       </c>
       <c r="R28" t="n">
-        <v>6665288</v>
+        <v>6665286</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3690,7 +3695,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3700,12 +3705,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Barkfläk, hagelsalva.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3732,10 +3737,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131255910</v>
+        <v>131256649</v>
       </c>
       <c r="B29" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3767,10 +3772,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488763</v>
+        <v>488685</v>
       </c>
       <c r="R29" t="n">
-        <v>6665157</v>
+        <v>6665288</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3802,7 +3807,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3812,12 +3817,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Tall.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3844,10 +3849,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131258531</v>
+        <v>131255910</v>
       </c>
       <c r="B30" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3879,10 +3884,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488725</v>
+        <v>488763</v>
       </c>
       <c r="R30" t="n">
-        <v>6665212</v>
+        <v>6665157</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3914,7 +3919,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3924,12 +3929,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Tall.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3956,10 +3961,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131257239</v>
+        <v>131258531</v>
       </c>
       <c r="B31" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3967,39 +3972,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488852</v>
+        <v>488725</v>
       </c>
       <c r="R31" t="n">
-        <v>6665286</v>
+        <v>6665212</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4041,12 +4041,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Barkfläk, hagelsalva.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4073,10 +4073,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131257659</v>
+        <v>131258537</v>
       </c>
       <c r="B32" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4084,39 +4084,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488901</v>
+        <v>488726</v>
       </c>
       <c r="R32" t="n">
-        <v>6665222</v>
+        <v>6665209</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4148,7 +4143,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4158,12 +4153,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4190,10 +4185,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131258537</v>
+        <v>131255108</v>
       </c>
       <c r="B33" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4225,10 +4220,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488726</v>
+        <v>488978</v>
       </c>
       <c r="R33" t="n">
-        <v>6665209</v>
+        <v>6665417</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4260,7 +4255,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4270,12 +4265,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4302,10 +4297,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131255108</v>
+        <v>131257659</v>
       </c>
       <c r="B34" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4313,34 +4308,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488978</v>
+        <v>488901</v>
       </c>
       <c r="R34" t="n">
-        <v>6665417</v>
+        <v>6665222</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4417,7 +4417,7 @@
         <v>131257913</v>
       </c>
       <c r="B35" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>131256459</v>
       </c>
       <c r="B36" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>131257385</v>
       </c>
       <c r="B37" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>131260531</v>
       </c>
       <c r="B38" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>131257731</v>
       </c>
       <c r="B39" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>131257440</v>
       </c>
       <c r="B40" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5087,10 +5087,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131257035</v>
+        <v>131257343</v>
       </c>
       <c r="B41" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5098,34 +5098,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488760</v>
+        <v>488872</v>
       </c>
       <c r="R41" t="n">
-        <v>6665301</v>
+        <v>6665191</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5157,7 +5162,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5167,12 +5172,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5199,10 +5204,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131257343</v>
+        <v>131257035</v>
       </c>
       <c r="B42" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5210,39 +5215,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488872</v>
+        <v>488760</v>
       </c>
       <c r="R42" t="n">
-        <v>6665191</v>
+        <v>6665301</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5319,7 +5319,7 @@
         <v>131273946</v>
       </c>
       <c r="B43" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>131273991</v>
       </c>
       <c r="B44" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>131273940</v>
       </c>
       <c r="B45" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 11705-2024 artfynd.xlsx
+++ b/artfynd/A 11705-2024 artfynd.xlsx
@@ -1027,7 +1027,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131256691</v>
+        <v>131260583</v>
       </c>
       <c r="B5" t="n">
         <v>57902</v>
@@ -1058,7 +1058,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488667</v>
+        <v>488834</v>
       </c>
       <c r="R5" t="n">
-        <v>6665262</v>
+        <v>6665228</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,12 +1112,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131260583</v>
+        <v>131255793</v>
       </c>
       <c r="B6" t="n">
-        <v>57902</v>
+        <v>91852</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,39 +1155,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488834</v>
+        <v>488817</v>
       </c>
       <c r="R6" t="n">
-        <v>6665228</v>
+        <v>6665110</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1219,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1229,12 +1220,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1373,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131255793</v>
+        <v>131256691</v>
       </c>
       <c r="B8" t="n">
-        <v>91852</v>
+        <v>57902</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1384,30 +1375,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488817</v>
+        <v>488667</v>
       </c>
       <c r="R8" t="n">
-        <v>6665110</v>
+        <v>6665262</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1710,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131260641</v>
+        <v>131256730</v>
       </c>
       <c r="B11" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1721,39 +1721,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488859</v>
+        <v>488689</v>
       </c>
       <c r="R11" t="n">
-        <v>6665292</v>
+        <v>6665231</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1785,7 +1780,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,12 +1790,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131257290</v>
+        <v>131257520</v>
       </c>
       <c r="B12" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,39 +1833,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488842</v>
+        <v>488939</v>
       </c>
       <c r="R12" t="n">
-        <v>6665224</v>
+        <v>6665149</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1902,7 +1892,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,12 +1902,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,7 +1934,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131256673</v>
+        <v>131260641</v>
       </c>
       <c r="B13" t="n">
         <v>57902</v>
@@ -1984,10 +1974,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488652</v>
+        <v>488859</v>
       </c>
       <c r="R13" t="n">
-        <v>6665282</v>
+        <v>6665292</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2019,7 +2009,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2029,12 +2019,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,10 +2051,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131256730</v>
+        <v>131257290</v>
       </c>
       <c r="B14" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2072,34 +2062,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488689</v>
+        <v>488842</v>
       </c>
       <c r="R14" t="n">
-        <v>6665231</v>
+        <v>6665224</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2131,7 +2126,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2141,12 +2136,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,10 +2168,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131257520</v>
+        <v>131256673</v>
       </c>
       <c r="B15" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2184,34 +2179,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488939</v>
+        <v>488652</v>
       </c>
       <c r="R15" t="n">
-        <v>6665149</v>
+        <v>6665282</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131255096</v>
+        <v>131257479</v>
       </c>
       <c r="B16" t="n">
-        <v>79264</v>
+        <v>91852</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2296,23 +2296,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2320,10 +2316,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488961</v>
+        <v>488908</v>
       </c>
       <c r="R16" t="n">
-        <v>6665423</v>
+        <v>6665154</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2355,7 +2351,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2365,12 +2361,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Stambrott. Hängande låga.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2397,10 +2393,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131257479</v>
+        <v>131255096</v>
       </c>
       <c r="B17" t="n">
-        <v>91852</v>
+        <v>79264</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2408,19 +2404,23 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488908</v>
+        <v>488961</v>
       </c>
       <c r="R17" t="n">
-        <v>6665154</v>
+        <v>6665423</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Stambrott. Hängande låga.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2953,10 +2953,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131257316</v>
+        <v>131255771</v>
       </c>
       <c r="B22" t="n">
-        <v>79264</v>
+        <v>81249</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2964,21 +2964,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488852</v>
+        <v>488818</v>
       </c>
       <c r="R22" t="n">
-        <v>6665209</v>
+        <v>6665110</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3033,12 +3033,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3065,10 +3060,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131255771</v>
+        <v>131257316</v>
       </c>
       <c r="B23" t="n">
-        <v>81249</v>
+        <v>79264</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3076,21 +3071,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3100,10 +3095,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488818</v>
+        <v>488852</v>
       </c>
       <c r="R23" t="n">
-        <v>6665110</v>
+        <v>6665209</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3135,7 +3130,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3145,7 +3140,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3620,10 +3620,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131257239</v>
+        <v>131256649</v>
       </c>
       <c r="B28" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3631,39 +3631,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488852</v>
+        <v>488685</v>
       </c>
       <c r="R28" t="n">
-        <v>6665286</v>
+        <v>6665288</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3695,7 +3690,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3705,12 +3700,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Barkfläk, hagelsalva.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3737,7 +3732,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131256649</v>
+        <v>131255910</v>
       </c>
       <c r="B29" t="n">
         <v>79264</v>
@@ -3772,10 +3767,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488685</v>
+        <v>488763</v>
       </c>
       <c r="R29" t="n">
-        <v>6665288</v>
+        <v>6665157</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3807,7 +3802,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3817,12 +3812,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Tall.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3849,7 +3844,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131255910</v>
+        <v>131258531</v>
       </c>
       <c r="B30" t="n">
         <v>79264</v>
@@ -3884,10 +3879,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488763</v>
+        <v>488725</v>
       </c>
       <c r="R30" t="n">
-        <v>6665157</v>
+        <v>6665212</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3919,7 +3914,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3929,12 +3924,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3961,10 +3956,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131258531</v>
+        <v>131257239</v>
       </c>
       <c r="B31" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3972,34 +3967,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488725</v>
+        <v>488852</v>
       </c>
       <c r="R31" t="n">
-        <v>6665212</v>
+        <v>6665286</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4041,12 +4041,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Barkfläk, hagelsalva.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4526,10 +4526,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131256459</v>
+        <v>131257385</v>
       </c>
       <c r="B36" t="n">
-        <v>57899</v>
+        <v>91852</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4537,39 +4537,30 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488669</v>
+        <v>488876</v>
       </c>
       <c r="R36" t="n">
-        <v>6665268</v>
+        <v>6665194</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4601,7 +4592,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4611,12 +4602,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska och äldre hack.</t>
+          <t>Lågstubbe.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4643,10 +4634,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131257385</v>
+        <v>131256459</v>
       </c>
       <c r="B37" t="n">
-        <v>91852</v>
+        <v>57899</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4654,30 +4645,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488876</v>
+        <v>488669</v>
       </c>
       <c r="R37" t="n">
-        <v>6665194</v>
+        <v>6665268</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4719,12 +4719,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Lågstubbe.</t>
+          <t>Färska och äldre hack.</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 11705-2024 artfynd.xlsx
+++ b/artfynd/A 11705-2024 artfynd.xlsx
@@ -1027,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131260583</v>
+        <v>131257424</v>
       </c>
       <c r="B5" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,39 +1038,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488834</v>
+        <v>488876</v>
       </c>
       <c r="R5" t="n">
-        <v>6665228</v>
+        <v>6665177</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,7 +1097,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,12 +1107,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1252,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131257424</v>
+        <v>131256691</v>
       </c>
       <c r="B7" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1263,34 +1258,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488876</v>
+        <v>488667</v>
       </c>
       <c r="R7" t="n">
-        <v>6665177</v>
+        <v>6665262</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,7 +1364,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131256691</v>
+        <v>131260583</v>
       </c>
       <c r="B8" t="n">
         <v>57902</v>
@@ -1395,7 +1395,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488667</v>
+        <v>488834</v>
       </c>
       <c r="R8" t="n">
-        <v>6665262</v>
+        <v>6665228</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131256423</v>
+        <v>131257188</v>
       </c>
       <c r="B9" t="n">
-        <v>57899</v>
+        <v>91852</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,51 +1492,33 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488671</v>
+        <v>488804</v>
       </c>
       <c r="R9" t="n">
-        <v>6665267</v>
+        <v>6665288</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1565,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1575,7 +1557,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1602,10 +1589,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131257188</v>
+        <v>131256423</v>
       </c>
       <c r="B10" t="n">
-        <v>91852</v>
+        <v>57899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,33 +1600,51 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488804</v>
+        <v>488671</v>
       </c>
       <c r="R10" t="n">
-        <v>6665288</v>
+        <v>6665267</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1668,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,12 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131256730</v>
+        <v>131260641</v>
       </c>
       <c r="B11" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1721,34 +1721,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488689</v>
+        <v>488859</v>
       </c>
       <c r="R11" t="n">
-        <v>6665231</v>
+        <v>6665292</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1780,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1790,12 +1795,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131257520</v>
+        <v>131257290</v>
       </c>
       <c r="B12" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1833,34 +1838,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488939</v>
+        <v>488842</v>
       </c>
       <c r="R12" t="n">
-        <v>6665149</v>
+        <v>6665224</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1892,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1902,12 +1912,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,7 +1944,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131260641</v>
+        <v>131256673</v>
       </c>
       <c r="B13" t="n">
         <v>57902</v>
@@ -1974,10 +1984,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488859</v>
+        <v>488652</v>
       </c>
       <c r="R13" t="n">
-        <v>6665292</v>
+        <v>6665282</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2009,7 +2019,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2019,12 +2029,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,10 +2061,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131257290</v>
+        <v>131257520</v>
       </c>
       <c r="B14" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2062,39 +2072,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488842</v>
+        <v>488939</v>
       </c>
       <c r="R14" t="n">
-        <v>6665224</v>
+        <v>6665149</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2126,7 +2131,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2136,12 +2141,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,10 +2173,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131256673</v>
+        <v>131256730</v>
       </c>
       <c r="B15" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2179,39 +2184,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488652</v>
+        <v>488689</v>
       </c>
       <c r="R15" t="n">
-        <v>6665282</v>
+        <v>6665231</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131257479</v>
+        <v>131255096</v>
       </c>
       <c r="B16" t="n">
-        <v>91852</v>
+        <v>79264</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2296,19 +2296,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2316,10 +2320,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488908</v>
+        <v>488961</v>
       </c>
       <c r="R16" t="n">
-        <v>6665154</v>
+        <v>6665423</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2351,7 +2355,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2361,12 +2365,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Stambrott. Hängande låga.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2393,7 +2397,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131255096</v>
+        <v>131256750</v>
       </c>
       <c r="B17" t="n">
         <v>79264</v>
@@ -2428,10 +2432,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488961</v>
+        <v>488704</v>
       </c>
       <c r="R17" t="n">
-        <v>6665423</v>
+        <v>6665241</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2463,7 +2467,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2473,12 +2477,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2505,10 +2509,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131256750</v>
+        <v>131257479</v>
       </c>
       <c r="B18" t="n">
-        <v>79264</v>
+        <v>91852</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,23 +2520,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488704</v>
+        <v>488908</v>
       </c>
       <c r="R18" t="n">
-        <v>6665241</v>
+        <v>6665154</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Stambrott. Hängande låga.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2617,7 +2617,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131256401</v>
+        <v>131256403</v>
       </c>
       <c r="B19" t="n">
         <v>79264</v>
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488679</v>
+        <v>488680</v>
       </c>
       <c r="R19" t="n">
-        <v>6665255</v>
+        <v>6665257</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2729,7 +2729,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131256403</v>
+        <v>131256401</v>
       </c>
       <c r="B20" t="n">
         <v>79264</v>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488680</v>
+        <v>488679</v>
       </c>
       <c r="R20" t="n">
-        <v>6665257</v>
+        <v>6665255</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3844,10 +3844,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131258531</v>
+        <v>131257239</v>
       </c>
       <c r="B30" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3855,34 +3855,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488725</v>
+        <v>488852</v>
       </c>
       <c r="R30" t="n">
-        <v>6665212</v>
+        <v>6665286</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3914,7 +3919,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3924,12 +3929,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Barkfläk, hagelsalva.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3956,10 +3961,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131257239</v>
+        <v>131258531</v>
       </c>
       <c r="B31" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3967,39 +3972,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488852</v>
+        <v>488725</v>
       </c>
       <c r="R31" t="n">
-        <v>6665286</v>
+        <v>6665212</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4041,12 +4041,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Barkfläk, hagelsalva.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4073,7 +4073,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131258537</v>
+        <v>131255108</v>
       </c>
       <c r="B32" t="n">
         <v>79264</v>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488726</v>
+        <v>488978</v>
       </c>
       <c r="R32" t="n">
-        <v>6665209</v>
+        <v>6665417</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4185,7 +4185,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131255108</v>
+        <v>131258537</v>
       </c>
       <c r="B33" t="n">
         <v>79264</v>
@@ -4220,10 +4220,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488978</v>
+        <v>488726</v>
       </c>
       <c r="R33" t="n">
-        <v>6665417</v>
+        <v>6665209</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4265,12 +4265,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5087,10 +5087,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131257343</v>
+        <v>131257035</v>
       </c>
       <c r="B41" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5098,39 +5098,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488872</v>
+        <v>488760</v>
       </c>
       <c r="R41" t="n">
-        <v>6665191</v>
+        <v>6665301</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5162,7 +5157,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5172,12 +5167,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5204,10 +5199,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131257035</v>
+        <v>131257343</v>
       </c>
       <c r="B42" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5215,34 +5210,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488760</v>
+        <v>488872</v>
       </c>
       <c r="R42" t="n">
-        <v>6665301</v>
+        <v>6665191</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5316,7 +5316,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131273946</v>
+        <v>131273991</v>
       </c>
       <c r="B43" t="n">
         <v>79264</v>
@@ -5354,10 +5354,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488774</v>
+        <v>488928</v>
       </c>
       <c r="R43" t="n">
-        <v>6665353</v>
+        <v>6665146</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -5417,7 +5417,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131273991</v>
+        <v>131273946</v>
       </c>
       <c r="B44" t="n">
         <v>79264</v>
@@ -5455,10 +5455,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488928</v>
+        <v>488774</v>
       </c>
       <c r="R44" t="n">
-        <v>6665146</v>
+        <v>6665353</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>

--- a/artfynd/A 11705-2024 artfynd.xlsx
+++ b/artfynd/A 11705-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>247999</v>
+        <v>131255771</v>
       </c>
       <c r="B2" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vaskolet 500 m väst om Gettjärn, Dlr</t>
+          <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489157.0199921019</v>
+        <v>488818</v>
       </c>
       <c r="R2" t="n">
-        <v>6665557.349159166</v>
+        <v>6665110</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1988-01-01</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1988-12-31</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,76 +767,60 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>björk i sumpgranskog på ved</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>Uppsala-Evolutionsmuseet</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131257487</v>
+        <v>131255096</v>
       </c>
       <c r="B3" t="n">
-        <v>57902</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488926</v>
+        <v>488961</v>
       </c>
       <c r="R3" t="n">
-        <v>6665146</v>
+        <v>6665423</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -873,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,12 +862,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,14 +894,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131257646</v>
+        <v>131255108</v>
       </c>
       <c r="B4" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -950,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488914</v>
+        <v>488978</v>
       </c>
       <c r="R4" t="n">
-        <v>6665193</v>
+        <v>6665417</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -985,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,12 +974,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,14 +1006,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131257424</v>
+        <v>131255910</v>
       </c>
       <c r="B5" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1062,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488876</v>
+        <v>488763</v>
       </c>
       <c r="R5" t="n">
-        <v>6665177</v>
+        <v>6665157</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1107,12 +1086,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,30 +1118,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131255793</v>
+        <v>131256338</v>
       </c>
       <c r="B6" t="n">
-        <v>91852</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1170,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488817</v>
+        <v>488693</v>
       </c>
       <c r="R6" t="n">
-        <v>6665110</v>
+        <v>6665189</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1215,12 +1198,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,50 +1230,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131256691</v>
+        <v>131256343</v>
       </c>
       <c r="B7" t="n">
-        <v>57902</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488667</v>
+        <v>488691</v>
       </c>
       <c r="R7" t="n">
-        <v>6665262</v>
+        <v>6665194</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1322,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,12 +1310,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Gran. Flera träd.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,50 +1342,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131260583</v>
+        <v>131256401</v>
       </c>
       <c r="B8" t="n">
-        <v>57902</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488834</v>
+        <v>488679</v>
       </c>
       <c r="R8" t="n">
-        <v>6665228</v>
+        <v>6665255</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1439,7 +1412,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1449,12 +1422,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,30 +1454,34 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131257188</v>
+        <v>131256403</v>
       </c>
       <c r="B9" t="n">
-        <v>91852</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1512,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488804</v>
+        <v>488680</v>
       </c>
       <c r="R9" t="n">
-        <v>6665288</v>
+        <v>6665257</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1547,7 +1524,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,12 +1534,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,62 +1566,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131256423</v>
+        <v>131256603</v>
       </c>
       <c r="B10" t="n">
-        <v>57899</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488671</v>
+        <v>488625</v>
       </c>
       <c r="R10" t="n">
-        <v>6665267</v>
+        <v>6665252</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,7 +1636,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1646,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,50 +1678,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131260641</v>
+        <v>131256649</v>
       </c>
       <c r="B11" t="n">
-        <v>57902</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488859</v>
+        <v>488685</v>
       </c>
       <c r="R11" t="n">
-        <v>6665292</v>
+        <v>6665288</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1785,7 +1748,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,12 +1758,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,50 +1790,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131257290</v>
+        <v>131256730</v>
       </c>
       <c r="B12" t="n">
-        <v>57902</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488842</v>
+        <v>488689</v>
       </c>
       <c r="R12" t="n">
-        <v>6665224</v>
+        <v>6665231</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1902,7 +1860,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,12 +1870,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,50 +1902,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131256673</v>
+        <v>131256750</v>
       </c>
       <c r="B13" t="n">
-        <v>57902</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488652</v>
+        <v>488704</v>
       </c>
       <c r="R13" t="n">
-        <v>6665282</v>
+        <v>6665241</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2019,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2029,12 +1982,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,14 +2014,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131257520</v>
+        <v>131257035</v>
       </c>
       <c r="B14" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2096,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488939</v>
+        <v>488760</v>
       </c>
       <c r="R14" t="n">
-        <v>6665149</v>
+        <v>6665301</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2131,7 +2084,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2141,7 +2094,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2173,14 +2126,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131256730</v>
+        <v>131257045</v>
       </c>
       <c r="B15" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2208,10 +2161,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488689</v>
+        <v>488760</v>
       </c>
       <c r="R15" t="n">
-        <v>6665231</v>
+        <v>6665302</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2243,7 +2196,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2253,7 +2206,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2285,14 +2238,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131255096</v>
+        <v>131257316</v>
       </c>
       <c r="B16" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2320,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488961</v>
+        <v>488852</v>
       </c>
       <c r="R16" t="n">
-        <v>6665423</v>
+        <v>6665209</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2355,7 +2308,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2365,12 +2318,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2397,14 +2350,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131256750</v>
+        <v>131257424</v>
       </c>
       <c r="B17" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2432,10 +2385,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488704</v>
+        <v>488876</v>
       </c>
       <c r="R17" t="n">
-        <v>6665241</v>
+        <v>6665177</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2467,7 +2420,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2477,7 +2430,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2509,30 +2462,34 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131257479</v>
+        <v>131257440</v>
       </c>
       <c r="B18" t="n">
-        <v>91852</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2540,10 +2497,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488908</v>
+        <v>488885</v>
       </c>
       <c r="R18" t="n">
-        <v>6665154</v>
+        <v>6665181</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2575,7 +2532,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2585,12 +2542,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Stambrott. Hängande låga.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2617,14 +2574,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131256403</v>
+        <v>131257520</v>
       </c>
       <c r="B19" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2652,10 +2609,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488680</v>
+        <v>488939</v>
       </c>
       <c r="R19" t="n">
-        <v>6665257</v>
+        <v>6665149</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2687,7 +2644,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2697,7 +2654,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2729,14 +2686,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131256401</v>
+        <v>131257544</v>
       </c>
       <c r="B20" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2764,10 +2721,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488679</v>
+        <v>488940</v>
       </c>
       <c r="R20" t="n">
-        <v>6665255</v>
+        <v>6665149</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2799,7 +2756,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2809,7 +2766,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2844,11 +2801,11 @@
         <v>131257637</v>
       </c>
       <c r="B21" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2953,32 +2910,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131255771</v>
+        <v>131257642</v>
       </c>
       <c r="B22" t="n">
-        <v>81249</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2988,10 +2945,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488818</v>
+        <v>488913</v>
       </c>
       <c r="R22" t="n">
-        <v>6665110</v>
+        <v>6665191</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3023,7 +2980,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3033,7 +2990,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3060,14 +3022,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131257316</v>
+        <v>131257646</v>
       </c>
       <c r="B23" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3095,10 +3057,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488852</v>
+        <v>488914</v>
       </c>
       <c r="R23" t="n">
-        <v>6665209</v>
+        <v>6665193</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3130,7 +3092,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3140,7 +3102,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3172,14 +3134,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131257642</v>
+        <v>131257650</v>
       </c>
       <c r="B24" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3207,10 +3169,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488913</v>
+        <v>488911</v>
       </c>
       <c r="R24" t="n">
-        <v>6665191</v>
+        <v>6665227</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3242,7 +3204,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3252,7 +3214,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3284,14 +3246,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131257045</v>
+        <v>131257731</v>
       </c>
       <c r="B25" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3319,10 +3281,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488760</v>
+        <v>488874</v>
       </c>
       <c r="R25" t="n">
-        <v>6665302</v>
+        <v>6665272</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3354,7 +3316,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3364,12 +3326,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3396,14 +3358,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131257650</v>
+        <v>131257913</v>
       </c>
       <c r="B26" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3431,10 +3393,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488911</v>
+        <v>488913</v>
       </c>
       <c r="R26" t="n">
-        <v>6665227</v>
+        <v>6665358</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3466,7 +3428,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3476,7 +3438,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3508,14 +3470,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131257544</v>
+        <v>131258531</v>
       </c>
       <c r="B27" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3543,10 +3505,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488940</v>
+        <v>488725</v>
       </c>
       <c r="R27" t="n">
-        <v>6665149</v>
+        <v>6665212</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3578,7 +3540,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3588,7 +3550,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3620,14 +3582,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131256649</v>
+        <v>131258537</v>
       </c>
       <c r="B28" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3655,10 +3617,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488685</v>
+        <v>488726</v>
       </c>
       <c r="R28" t="n">
-        <v>6665288</v>
+        <v>6665209</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3690,7 +3652,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3700,12 +3662,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3732,14 +3694,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131255910</v>
+        <v>131260531</v>
       </c>
       <c r="B29" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3767,10 +3729,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488763</v>
+        <v>488786</v>
       </c>
       <c r="R29" t="n">
-        <v>6665157</v>
+        <v>6665188</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3802,7 +3764,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3812,12 +3774,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3844,53 +3806,51 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131257239</v>
+        <v>131273940</v>
       </c>
       <c r="B30" t="n">
-        <v>57902</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hyttfallet, Hyttfallet, Dlr</t>
+          <t>Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488852</v>
+        <v>488785</v>
       </c>
       <c r="R30" t="n">
-        <v>6665286</v>
+        <v>6665325</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3917,58 +3877,44 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Barkfläk, hagelsalva.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131258531</v>
+        <v>131273946</v>
       </c>
       <c r="B31" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3990,19 +3936,22 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hyttfallet, Hyttfallet, Dlr</t>
+          <t>Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488725</v>
+        <v>488774</v>
       </c>
       <c r="R31" t="n">
-        <v>6665212</v>
+        <v>6665353</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4029,58 +3978,44 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131255108</v>
+        <v>131273991</v>
       </c>
       <c r="B32" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -4102,19 +4037,22 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hyttfallet, Hyttfallet, Dlr</t>
+          <t>Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488978</v>
+        <v>488928</v>
       </c>
       <c r="R32" t="n">
-        <v>6665417</v>
+        <v>6665146</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4141,92 +4079,92 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>09:08</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>09:08</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Gran.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131258537</v>
+        <v>131256423</v>
       </c>
       <c r="B33" t="n">
-        <v>79264</v>
+        <v>57950</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488726</v>
+        <v>488671</v>
       </c>
       <c r="R33" t="n">
-        <v>6665209</v>
+        <v>6665267</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4255,7 +4193,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4265,12 +4203,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4297,27 +4230,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131257659</v>
+        <v>131256459</v>
       </c>
       <c r="B34" t="n">
-        <v>57902</v>
+        <v>57950</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4328,7 +4261,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4337,10 +4270,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488901</v>
+        <v>488669</v>
       </c>
       <c r="R34" t="n">
-        <v>6665222</v>
+        <v>6665268</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4372,7 +4305,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4382,12 +4315,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Färska och äldre hack.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4414,10 +4347,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131257913</v>
+        <v>131256256</v>
       </c>
       <c r="B35" t="n">
-        <v>79264</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4425,34 +4358,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488913</v>
+        <v>488691</v>
       </c>
       <c r="R35" t="n">
-        <v>6665358</v>
+        <v>6665177</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4484,7 +4422,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4494,12 +4432,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4526,10 +4464,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131257385</v>
+        <v>131256516</v>
       </c>
       <c r="B36" t="n">
-        <v>91852</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4537,30 +4475,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488876</v>
+        <v>488625</v>
       </c>
       <c r="R36" t="n">
-        <v>6665194</v>
+        <v>6665252</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4592,7 +4539,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4602,12 +4549,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Lågstubbe.</t>
+          <t>Rikligt hackad. Tall.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4634,10 +4581,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131256459</v>
+        <v>131256673</v>
       </c>
       <c r="B37" t="n">
-        <v>57899</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4645,16 +4592,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4665,7 +4612,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4674,10 +4621,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488669</v>
+        <v>488652</v>
       </c>
       <c r="R37" t="n">
-        <v>6665268</v>
+        <v>6665282</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4709,7 +4656,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4719,12 +4666,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska och äldre hack.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4751,10 +4698,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131260531</v>
+        <v>131256691</v>
       </c>
       <c r="B38" t="n">
-        <v>79264</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4762,34 +4709,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488786</v>
+        <v>488667</v>
       </c>
       <c r="R38" t="n">
-        <v>6665188</v>
+        <v>6665262</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4821,7 +4773,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4831,12 +4783,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4863,10 +4815,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131257731</v>
+        <v>131257239</v>
       </c>
       <c r="B39" t="n">
-        <v>79264</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4874,34 +4826,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488874</v>
+        <v>488852</v>
       </c>
       <c r="R39" t="n">
-        <v>6665272</v>
+        <v>6665286</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4933,7 +4890,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4943,12 +4900,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Barkfläk, hagelsalva.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4975,10 +4932,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131257440</v>
+        <v>131257290</v>
       </c>
       <c r="B40" t="n">
-        <v>79264</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4986,34 +4943,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488885</v>
+        <v>488842</v>
       </c>
       <c r="R40" t="n">
-        <v>6665181</v>
+        <v>6665224</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5045,7 +5007,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5055,12 +5017,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5087,10 +5049,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131257035</v>
+        <v>131257343</v>
       </c>
       <c r="B41" t="n">
-        <v>79264</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5098,34 +5060,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488760</v>
+        <v>488872</v>
       </c>
       <c r="R41" t="n">
-        <v>6665301</v>
+        <v>6665191</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5157,7 +5124,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5167,12 +5134,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5199,10 +5166,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131257343</v>
+        <v>131257487</v>
       </c>
       <c r="B42" t="n">
-        <v>57902</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5230,7 +5197,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5239,10 +5206,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488872</v>
+        <v>488926</v>
       </c>
       <c r="R42" t="n">
-        <v>6665191</v>
+        <v>6665146</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5274,7 +5241,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5284,12 +5251,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5316,10 +5283,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131273991</v>
+        <v>131257659</v>
       </c>
       <c r="B43" t="n">
-        <v>79264</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5327,40 +5294,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hyttfallet, Dlr</t>
+          <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488928</v>
+        <v>488901</v>
       </c>
       <c r="R43" t="n">
-        <v>6665146</v>
+        <v>6665222</v>
       </c>
       <c r="S43" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5387,40 +5356,54 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131273946</v>
+        <v>131260583</v>
       </c>
       <c r="B44" t="n">
-        <v>79264</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5428,40 +5411,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hyttfallet, Dlr</t>
+          <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488774</v>
+        <v>488834</v>
       </c>
       <c r="R44" t="n">
-        <v>6665353</v>
+        <v>6665228</v>
       </c>
       <c r="S44" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5488,40 +5473,54 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131273940</v>
+        <v>131260641</v>
       </c>
       <c r="B45" t="n">
-        <v>79264</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5529,40 +5528,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hyttfallet, Dlr</t>
+          <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488785</v>
+        <v>488859</v>
       </c>
       <c r="R45" t="n">
-        <v>6665325</v>
+        <v>6665292</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5589,33 +5590,157 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>131267934</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Hyttfallet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>488711</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6665178</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ett fåtal korta hackrader på äldre tall.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
           <t>Anna-Lena Thommson</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
+      <c r="AX46" t="inlineStr">
         <is>
           <t>Anna-Lena Thommson</t>
         </is>
       </c>
-      <c r="AY45" t="inlineStr"/>
+      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
